--- a/db/A7XLK-1301-Bus.xlsx
+++ b/db/A7XLK-1301-Bus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.1_AiCity2019/AiCity2019/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494DCABC-C15F-FD48-828A-CE994C735F82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A885D962-3FEF-0A45-9BE7-C69A2A4CA04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="48220" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="500" windowWidth="39980" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="251">
   <si>
     <t>No</t>
   </si>
@@ -740,13 +740,57 @@
   </si>
   <si>
     <t>090</t>
+  </si>
+  <si>
+    <t>966 副</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>967 副</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>937 副</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>920 副</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口轉運站</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:00 - 20:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>05:40 - 19:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>板橋公車站</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/EBus/VsSimpleMap?routeid=0400094800&amp;amp;gb=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/EBus/VsSimpleMap?routeid=0400094800&amp;gb=1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/MapOverview?nid=0400094800</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -764,6 +808,20 @@
       <name val="Wawati TC"/>
       <family val="3"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -783,16 +841,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1092,28 +1155,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="8.83203125" style="2"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.5" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="3" max="3" width="10" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="48.33203125" customWidth="1"/>
-    <col min="7" max="7" width="67" customWidth="1"/>
+    <col min="7" max="7" width="53.33203125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="10" max="10" width="16.5" customWidth="1"/>
-    <col min="11" max="11" width="49.1640625" customWidth="1"/>
+    <col min="11" max="11" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1142,13 +1206,13 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>11</v>
+      <c r="A2" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D2" t="s">
@@ -1174,189 +1238,189 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>21</v>
+      <c r="A3" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>23</v>
+      <c r="A4" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
+      <c r="C4" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>113</v>
+      </c>
+      <c r="K4" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>30</v>
+      <c r="A5" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="K5" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>38</v>
+      <c r="A6" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>44</v>
+      <c r="A7" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>45</v>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>49</v>
+      <c r="A8" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -1371,27 +1435,27 @@
         <v>35</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>51</v>
+      <c r="A9" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>52</v>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -1403,30 +1467,30 @@
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>55</v>
+      <c r="A10" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>56</v>
+      <c r="C10" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -1441,27 +1505,27 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>60</v>
+      <c r="A11" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" t="s">
-        <v>61</v>
+      <c r="C11" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
         <v>34</v>
@@ -1475,25 +1539,25 @@
       <c r="I11" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="1">
-        <v>0.69791666666666696</v>
+      <c r="J11" t="s">
+        <v>53</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>64</v>
+      <c r="A12" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
-        <v>65</v>
+      <c r="C12" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
         <v>57</v>
@@ -1510,28 +1574,28 @@
       <c r="I12" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="1">
-        <v>0.30555555555555602</v>
+      <c r="J12" t="s">
+        <v>58</v>
       </c>
       <c r="K12" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>68</v>
+      <c r="A13" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
-        <v>69</v>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
         <v>34</v>
@@ -1545,28 +1609,28 @@
       <c r="I13" t="s">
         <v>35</v>
       </c>
-      <c r="J13" t="s">
-        <v>72</v>
+      <c r="J13" s="1">
+        <v>0.69791666666666696</v>
       </c>
       <c r="K13" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>74</v>
+      <c r="A14" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
@@ -1580,28 +1644,28 @@
       <c r="I14" t="s">
         <v>35</v>
       </c>
-      <c r="J14" t="s">
-        <v>72</v>
+      <c r="J14" s="1">
+        <v>0.30555555555555602</v>
       </c>
       <c r="K14" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>75</v>
+      <c r="A15" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" t="s">
-        <v>76</v>
+      <c r="C15" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
@@ -1610,23 +1674,26 @@
         <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>35</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>72</v>
+      </c>
+      <c r="K15" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>80</v>
+      <c r="A16" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D16" t="s">
@@ -1652,13 +1719,13 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D17" t="s">
@@ -1687,13 +1754,13 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D18" t="s">
@@ -1722,13 +1789,13 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D19" t="s">
@@ -1757,14 +1824,14 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>97</v>
+      <c r="A20" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D20" t="s">
         <v>70</v>
@@ -1788,24 +1855,24 @@
         <v>95</v>
       </c>
       <c r="K20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>98</v>
+      <c r="A21" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21" t="s">
-        <v>99</v>
+      <c r="C21" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
@@ -1817,141 +1884,141 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J21" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K21" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>101</v>
+      <c r="A22" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
+        <v>12</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
         <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="K22" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>102</v>
+      <c r="A23" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
-      <c r="C23" t="s">
-        <v>103</v>
+      <c r="C23" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="K23" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>107</v>
+      <c r="A24" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>103</v>
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="K24" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>108</v>
+      <c r="A25" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
-      <c r="C25" t="s">
-        <v>109</v>
+      <c r="C25" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="G25" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
@@ -1960,33 +2027,33 @@
         <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="K25" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>115</v>
+      <c r="A26" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="G26" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
@@ -1995,450 +2062,453 @@
         <v>19</v>
       </c>
       <c r="J26" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="K26" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>116</v>
+      <c r="A27" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="G27" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="H27" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="J27" t="s">
         <v>113</v>
       </c>
       <c r="K27" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>117</v>
+      <c r="A28" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="H28" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="J28" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="K28" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>119</v>
+      <c r="A29" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
-      <c r="C29" t="s">
-        <v>120</v>
+      <c r="C29" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
       </c>
       <c r="J29" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="K29" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>126</v>
+      <c r="A30" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
+        <v>12</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>184</v>
       </c>
       <c r="H30" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="J30" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="K30" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>127</v>
+      <c r="A31" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
+        <v>12</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="F31" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="K31" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>128</v>
+      <c r="A32" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" t="s">
-        <v>120</v>
+        <v>12</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="F32" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="H32" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I32" t="s">
         <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>129</v>
+      <c r="A33" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
-      <c r="C33" t="s">
-        <v>130</v>
+      <c r="C33" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>190</v>
       </c>
       <c r="E33" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="F33" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="G33" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="H33" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I33" t="s">
         <v>19</v>
       </c>
       <c r="J33" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="K33" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>136</v>
+      <c r="A34" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
-      <c r="C34" t="s">
-        <v>137</v>
+      <c r="C34" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="D34" t="s">
         <v>138</v>
       </c>
       <c r="E34" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="F34" t="s">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="G34" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="H34" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="J34" t="s">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="K34" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>144</v>
+      <c r="A35" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" t="s">
-        <v>137</v>
+        <v>12</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>138</v>
+      </c>
+      <c r="E35" t="s">
+        <v>212</v>
       </c>
       <c r="F35" t="s">
-        <v>140</v>
+        <v>213</v>
       </c>
       <c r="G35" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I35" t="s">
         <v>19</v>
       </c>
       <c r="J35" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="K35" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>146</v>
+      <c r="A36" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
-      <c r="C36" t="s">
-        <v>147</v>
+      <c r="C36" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="E36" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="F36" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
       <c r="G36" t="s">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
       </c>
       <c r="J36" t="s">
-        <v>151</v>
+        <v>225</v>
       </c>
       <c r="K36" t="s">
-        <v>152</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>153</v>
+      <c r="A37" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" t="s">
-        <v>147</v>
+        <v>12</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="E37" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="F37" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
       <c r="G37" t="s">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="H37" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I37" t="s">
         <v>19</v>
       </c>
       <c r="J37" t="s">
-        <v>151</v>
+        <v>225</v>
       </c>
       <c r="K37" t="s">
-        <v>152</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>154</v>
+      <c r="A38" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>147</v>
+        <v>12</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="E38" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="F38" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
       <c r="G38" t="s">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
       </c>
       <c r="J38" t="s">
-        <v>151</v>
+        <v>225</v>
       </c>
       <c r="K38" t="s">
-        <v>152</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>155</v>
+      <c r="A39" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B39" t="s">
         <v>118</v>
       </c>
-      <c r="C39" t="s">
-        <v>147</v>
+      <c r="C39" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="G39" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
@@ -2447,418 +2517,415 @@
         <v>19</v>
       </c>
       <c r="J39" t="s">
+        <v>113</v>
+      </c>
+      <c r="K39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F40" t="s">
+        <v>122</v>
+      </c>
+      <c r="G40" t="s">
+        <v>123</v>
+      </c>
+      <c r="H40" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" t="s">
+        <v>124</v>
+      </c>
+      <c r="K40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" t="s">
+        <v>149</v>
+      </c>
+      <c r="G41" t="s">
+        <v>150</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" t="s">
         <v>151</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K41" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>156</v>
-      </c>
-      <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" t="s">
-        <v>157</v>
-      </c>
-      <c r="D40" t="s">
-        <v>138</v>
-      </c>
-      <c r="E40" t="s">
-        <v>158</v>
-      </c>
-      <c r="F40" t="s">
-        <v>159</v>
-      </c>
-      <c r="G40" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" t="s">
-        <v>161</v>
-      </c>
-      <c r="J40" t="s">
-        <v>113</v>
-      </c>
-      <c r="K40" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>163</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D42" t="s">
+        <v>221</v>
+      </c>
+      <c r="E42" t="s">
+        <v>222</v>
+      </c>
+      <c r="F42" t="s">
+        <v>223</v>
+      </c>
+      <c r="G42" t="s">
+        <v>224</v>
+      </c>
+      <c r="H42" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" t="s">
+        <v>225</v>
+      </c>
+      <c r="K42" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B43" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" t="s">
+        <v>221</v>
+      </c>
+      <c r="E43" t="s">
+        <v>222</v>
+      </c>
+      <c r="F43" t="s">
+        <v>223</v>
+      </c>
+      <c r="G43" t="s">
+        <v>224</v>
+      </c>
+      <c r="H43" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" t="s">
+        <v>225</v>
+      </c>
+      <c r="K43" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" t="s">
+        <v>222</v>
+      </c>
+      <c r="F44" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H44" t="s">
+        <v>28</v>
+      </c>
+      <c r="I44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" t="s">
+        <v>225</v>
+      </c>
+      <c r="K44" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" t="s">
+        <v>219</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" t="s">
+        <v>221</v>
+      </c>
+      <c r="E45" t="s">
+        <v>222</v>
+      </c>
+      <c r="F45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G45" t="s">
+        <v>224</v>
+      </c>
+      <c r="H45" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" t="s">
+        <v>225</v>
+      </c>
+      <c r="K45" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" t="s">
+        <v>222</v>
+      </c>
+      <c r="F46" t="s">
+        <v>223</v>
+      </c>
+      <c r="G46" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46" t="s">
+        <v>28</v>
+      </c>
+      <c r="I46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" t="s">
+        <v>225</v>
+      </c>
+      <c r="K46" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
         <v>50</v>
       </c>
-      <c r="C41" t="s">
-        <v>157</v>
-      </c>
-      <c r="D41" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" t="s">
-        <v>159</v>
-      </c>
-      <c r="G41" t="s">
-        <v>160</v>
-      </c>
-      <c r="H41" t="s">
-        <v>28</v>
-      </c>
-      <c r="I41" t="s">
-        <v>161</v>
-      </c>
-      <c r="J41" t="s">
-        <v>113</v>
-      </c>
-      <c r="K41" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>164</v>
-      </c>
-      <c r="B42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" t="s">
-        <v>138</v>
-      </c>
-      <c r="E42" t="s">
-        <v>166</v>
-      </c>
-      <c r="F42" t="s">
-        <v>167</v>
-      </c>
-      <c r="G42" t="s">
-        <v>168</v>
-      </c>
-      <c r="H42" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" t="s">
-        <v>161</v>
-      </c>
-      <c r="J42" t="s">
-        <v>169</v>
-      </c>
-      <c r="K42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>171</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="C47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" t="s">
+        <v>35</v>
+      </c>
+      <c r="J47" t="s">
+        <v>47</v>
+      </c>
+      <c r="K47" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" t="s">
         <v>50</v>
       </c>
-      <c r="C43" t="s">
-        <v>165</v>
-      </c>
-      <c r="D43" t="s">
-        <v>138</v>
-      </c>
-      <c r="E43" t="s">
-        <v>166</v>
-      </c>
-      <c r="F43" t="s">
-        <v>167</v>
-      </c>
-      <c r="G43" t="s">
-        <v>168</v>
-      </c>
-      <c r="H43" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" t="s">
-        <v>161</v>
-      </c>
-      <c r="J43" t="s">
-        <v>169</v>
-      </c>
-      <c r="K43" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>172</v>
-      </c>
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>173</v>
-      </c>
-      <c r="D44" t="s">
-        <v>174</v>
-      </c>
-      <c r="E44" t="s">
-        <v>175</v>
-      </c>
-      <c r="F44" t="s">
-        <v>176</v>
-      </c>
-      <c r="G44" t="s">
-        <v>177</v>
-      </c>
-      <c r="H44" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" t="s">
-        <v>178</v>
-      </c>
-      <c r="K44" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>180</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="C48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s">
+        <v>71</v>
+      </c>
+      <c r="F48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" t="s">
+        <v>35</v>
+      </c>
+      <c r="J48" t="s">
+        <v>72</v>
+      </c>
+      <c r="K48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
         <v>50</v>
       </c>
-      <c r="C45" t="s">
-        <v>173</v>
-      </c>
-      <c r="D45" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" t="s">
-        <v>175</v>
-      </c>
-      <c r="F45" t="s">
-        <v>176</v>
-      </c>
-      <c r="G45" t="s">
-        <v>177</v>
-      </c>
-      <c r="H45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I45" t="s">
-        <v>19</v>
-      </c>
-      <c r="J45" t="s">
-        <v>178</v>
-      </c>
-      <c r="K45" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>181</v>
-      </c>
-      <c r="B46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" t="s">
-        <v>182</v>
-      </c>
-      <c r="D46" t="s">
-        <v>138</v>
-      </c>
-      <c r="E46" t="s">
-        <v>175</v>
-      </c>
-      <c r="F46" t="s">
-        <v>183</v>
-      </c>
-      <c r="G46" t="s">
-        <v>184</v>
-      </c>
-      <c r="H46" t="s">
-        <v>28</v>
-      </c>
-      <c r="I46" t="s">
-        <v>185</v>
-      </c>
-      <c r="J46" t="s">
-        <v>186</v>
-      </c>
-      <c r="K46" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>188</v>
-      </c>
-      <c r="B47" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" t="s">
-        <v>190</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="C49" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" t="s">
         <v>78</v>
       </c>
-      <c r="F47" t="s">
-        <v>191</v>
-      </c>
-      <c r="G47" t="s">
-        <v>192</v>
-      </c>
-      <c r="H47" t="s">
-        <v>28</v>
-      </c>
-      <c r="I47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J47" t="s">
-        <v>193</v>
-      </c>
-      <c r="K47" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>195</v>
-      </c>
-      <c r="B48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" t="s">
-        <v>190</v>
-      </c>
-      <c r="E48" t="s">
-        <v>197</v>
-      </c>
-      <c r="F48" t="s">
-        <v>198</v>
-      </c>
-      <c r="G48" t="s">
-        <v>198</v>
-      </c>
-      <c r="H48" t="s">
-        <v>28</v>
-      </c>
-      <c r="I48" t="s">
-        <v>19</v>
-      </c>
-      <c r="J48" t="s">
-        <v>193</v>
-      </c>
-      <c r="K48" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>200</v>
-      </c>
-      <c r="B49" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" t="s">
-        <v>201</v>
-      </c>
-      <c r="D49" t="s">
-        <v>190</v>
-      </c>
-      <c r="E49" t="s">
-        <v>197</v>
-      </c>
       <c r="F49" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="G49" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="H49" t="s">
         <v>28</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J49" t="s">
-        <v>193</v>
-      </c>
-      <c r="K49" t="s">
-        <v>202</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>203</v>
+      <c r="A50" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" t="s">
-        <v>204</v>
+        <v>50</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>94</v>
       </c>
       <c r="F50" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="G50" t="s">
-        <v>207</v>
+        <v>34</v>
       </c>
       <c r="H50" t="s">
         <v>28</v>
       </c>
       <c r="I50" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="J50" t="s">
-        <v>208</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>210</v>
+      <c r="A51" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" t="s">
-        <v>211</v>
+        <v>50</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="E51" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="F51" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>214</v>
+        <v>34</v>
       </c>
       <c r="H51" t="s">
         <v>28</v>
@@ -2867,278 +2934,275 @@
         <v>19</v>
       </c>
       <c r="J51" t="s">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s">
-        <v>216</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>217</v>
+      <c r="A52" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B52" t="s">
         <v>50</v>
       </c>
-      <c r="C52" t="s">
-        <v>211</v>
+      <c r="C52" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="F52" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
       <c r="G52" t="s">
-        <v>214</v>
+        <v>34</v>
       </c>
       <c r="H52" t="s">
         <v>28</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J52" t="s">
-        <v>215</v>
+        <v>105</v>
       </c>
       <c r="K52" t="s">
-        <v>216</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>218</v>
+      <c r="A53" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>219</v>
-      </c>
-      <c r="C53" t="s">
-        <v>220</v>
+        <v>50</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D53" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="F53" t="s">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="G53" t="s">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="H53" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
       </c>
       <c r="J53" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="K53" t="s">
-        <v>226</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>227</v>
+      <c r="A54" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" t="s">
-        <v>220</v>
+        <v>50</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="E54" t="s">
-        <v>222</v>
+        <v>121</v>
       </c>
       <c r="F54" t="s">
-        <v>223</v>
+        <v>122</v>
       </c>
       <c r="G54" t="s">
-        <v>224</v>
+        <v>123</v>
       </c>
       <c r="H54" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
         <v>19</v>
       </c>
       <c r="J54" t="s">
-        <v>225</v>
+        <v>124</v>
       </c>
       <c r="K54" t="s">
-        <v>226</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>228</v>
+      <c r="A55" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="B55" t="s">
         <v>50</v>
       </c>
-      <c r="C55" t="s">
-        <v>220</v>
+      <c r="C55" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D55" t="s">
-        <v>221</v>
-      </c>
-      <c r="E55" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="F55" t="s">
-        <v>223</v>
+        <v>140</v>
       </c>
       <c r="G55" t="s">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="H55" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
       </c>
       <c r="J55" t="s">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="K55" t="s">
-        <v>226</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>229</v>
+      <c r="A56" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" t="s">
-        <v>220</v>
+        <v>50</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>222</v>
+        <v>148</v>
       </c>
       <c r="F56" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="G56" t="s">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="H56" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
       </c>
       <c r="J56" t="s">
-        <v>225</v>
+        <v>151</v>
       </c>
       <c r="K56" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>230</v>
+      <c r="A57" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
-      </c>
-      <c r="C57" t="s">
-        <v>231</v>
+        <v>50</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="D57" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>222</v>
+        <v>158</v>
       </c>
       <c r="F57" t="s">
-        <v>223</v>
+        <v>159</v>
       </c>
       <c r="G57" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="H57" t="s">
         <v>28</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="J57" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="K57" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>233</v>
+      <c r="A58" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" t="s">
-        <v>231</v>
+        <v>50</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="E58" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="G58" t="s">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="H58" t="s">
         <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="J58" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="K58" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>234</v>
+      <c r="A59" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="B59" t="s">
         <v>50</v>
       </c>
-      <c r="C59" t="s">
-        <v>231</v>
+      <c r="C59" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="D59" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="E59" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="F59" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="G59" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="H59" t="s">
         <v>28</v>
@@ -3147,33 +3211,33 @@
         <v>19</v>
       </c>
       <c r="J59" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="K59" t="s">
-        <v>232</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>235</v>
+      <c r="A60" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" t="s">
-        <v>231</v>
+        <v>50</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="D60" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="E60" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F60" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G60" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="H60" t="s">
         <v>28</v>
@@ -3182,21 +3246,21 @@
         <v>19</v>
       </c>
       <c r="J60" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="K60" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>236</v>
+      <c r="A61" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" t="s">
-        <v>237</v>
+        <v>50</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="D61" t="s">
         <v>221</v>
@@ -3220,18 +3284,18 @@
         <v>225</v>
       </c>
       <c r="K61" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>238</v>
+      <c r="A62" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="B62" t="s">
         <v>50</v>
       </c>
-      <c r="C62" t="s">
-        <v>237</v>
+      <c r="C62" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="D62" t="s">
         <v>221</v>
@@ -3259,13 +3323,13 @@
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>239</v>
+      <c r="A63" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="B63" t="s">
-        <v>118</v>
-      </c>
-      <c r="C63" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D63" t="s">
@@ -3293,8 +3357,287 @@
         <v>232</v>
       </c>
     </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>101</v>
+      </c>
+      <c r="B64" t="s">
+        <v>244</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" t="s">
+        <v>110</v>
+      </c>
+      <c r="F64" t="s">
+        <v>111</v>
+      </c>
+      <c r="G64" t="s">
+        <v>112</v>
+      </c>
+      <c r="H64" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" t="s">
+        <v>113</v>
+      </c>
+      <c r="K64" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>102</v>
+      </c>
+      <c r="B65" t="s">
+        <v>244</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" t="s">
+        <v>139</v>
+      </c>
+      <c r="F65" t="s">
+        <v>140</v>
+      </c>
+      <c r="G65" t="s">
+        <v>141</v>
+      </c>
+      <c r="H65" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" t="s">
+        <v>142</v>
+      </c>
+      <c r="K65" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>103</v>
+      </c>
+      <c r="B66" t="s">
+        <v>244</v>
+      </c>
+      <c r="C66" s="2">
+        <v>760</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="H66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>104</v>
+      </c>
+      <c r="B67" t="s">
+        <v>244</v>
+      </c>
+      <c r="C67" s="2">
+        <v>948</v>
+      </c>
+      <c r="D67" t="s">
+        <v>138</v>
+      </c>
+      <c r="E67" t="s">
+        <v>247</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H67" t="s">
+        <v>28</v>
+      </c>
+      <c r="I67" t="s">
+        <v>161</v>
+      </c>
+      <c r="J67" t="s">
+        <v>246</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>105</v>
+      </c>
+      <c r="B68" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E68" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" t="s">
+        <v>213</v>
+      </c>
+      <c r="G68" t="s">
+        <v>214</v>
+      </c>
+      <c r="H68" t="s">
+        <v>28</v>
+      </c>
+      <c r="I68" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" t="s">
+        <v>215</v>
+      </c>
+      <c r="K68" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>106</v>
+      </c>
+      <c r="B69" t="s">
+        <v>244</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E69" t="s">
+        <v>222</v>
+      </c>
+      <c r="F69" t="s">
+        <v>223</v>
+      </c>
+      <c r="G69" t="s">
+        <v>224</v>
+      </c>
+      <c r="H69" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" t="s">
+        <v>225</v>
+      </c>
+      <c r="K69" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>107</v>
+      </c>
+      <c r="B70" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E70" t="s">
+        <v>175</v>
+      </c>
+      <c r="F70" t="s">
+        <v>183</v>
+      </c>
+      <c r="G70" t="s">
+        <v>184</v>
+      </c>
+      <c r="H70" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" t="s">
+        <v>185</v>
+      </c>
+      <c r="J70" t="s">
+        <v>186</v>
+      </c>
+      <c r="K70" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>108</v>
+      </c>
+      <c r="B71" t="s">
+        <v>244</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" t="s">
+        <v>158</v>
+      </c>
+      <c r="F71" t="s">
+        <v>159</v>
+      </c>
+      <c r="G71" t="s">
+        <v>160</v>
+      </c>
+      <c r="H71" t="s">
+        <v>28</v>
+      </c>
+      <c r="I71" t="s">
+        <v>161</v>
+      </c>
+      <c r="J71" t="s">
+        <v>113</v>
+      </c>
+      <c r="K71" t="s">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K63">
+    <sortCondition ref="B2:B63"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="K67" r:id="rId1" xr:uid="{9879FFAF-1B89-4142-BC32-5F8FF16D1C65}"/>
+    <hyperlink ref="G67" r:id="rId2" xr:uid="{03C06EE7-B036-FD43-BE6D-03B1D0965FA4}"/>
+    <hyperlink ref="F67" r:id="rId3" xr:uid="{D816E695-43E8-B848-8865-24DFCE3DDE79}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/db/A7XLK-1301-Bus.xlsx
+++ b/db/A7XLK-1301-Bus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A885D962-3FEF-0A45-9BE7-C69A2A4CA04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1292A2-4A2F-D540-9DE1-8930D6086BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="39980" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2140" yWindow="2100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -37,12 +37,6 @@
     <t>訖站</t>
   </si>
   <si>
-    <t>即時資訊-返</t>
-  </si>
-  <si>
-    <t>即時資訊-出</t>
-  </si>
-  <si>
     <t>型態</t>
   </si>
   <si>
@@ -783,6 +777,14 @@
   </si>
   <si>
     <t>https://ebus.gov.taipei/MapOverview?nid=0400094800</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>即時資訊返</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>即時資訊出</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1187,2174 +1189,2174 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
         <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
         <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" t="s">
         <v>109</v>
       </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>110</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
         <v>111</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>112</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" t="s">
         <v>120</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>121</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
         <v>122</v>
       </c>
-      <c r="G5" t="s">
+      <c r="K5" t="s">
         <v>123</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>124</v>
-      </c>
-      <c r="K5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" t="s">
         <v>147</v>
       </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>148</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
         <v>149</v>
       </c>
-      <c r="G6" t="s">
+      <c r="K6" t="s">
         <v>150</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K6" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
         <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
         <v>33</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>34</v>
       </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>35</v>
-      </c>
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="J9" t="s">
         <v>40</v>
       </c>
-      <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="K10" t="s">
         <v>46</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" t="s">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="K11" t="s">
         <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>55</v>
       </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" t="s">
         <v>56</v>
       </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="K12" t="s">
         <v>57</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K12" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J13" s="1">
         <v>0.69791666666666696</v>
       </c>
       <c r="K13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
         <v>64</v>
       </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J14" s="1">
         <v>0.30555555555555602</v>
       </c>
       <c r="K14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
         <v>68</v>
       </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" t="s">
         <v>69</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" t="s">
         <v>70</v>
       </c>
-      <c r="E15" t="s">
+      <c r="K15" t="s">
         <v>71</v>
-      </c>
-      <c r="F15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" t="s">
-        <v>72</v>
-      </c>
-      <c r="K15" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
         <v>75</v>
       </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" t="s">
         <v>76</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" t="s">
         <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
         <v>81</v>
       </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
         <v>82</v>
       </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="J17" t="s">
         <v>83</v>
       </c>
-      <c r="F17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>84</v>
-      </c>
-      <c r="J17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
         <v>87</v>
       </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" t="s">
         <v>88</v>
       </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="K18" t="s">
         <v>89</v>
-      </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" t="s">
-        <v>84</v>
-      </c>
-      <c r="J18" t="s">
-        <v>90</v>
-      </c>
-      <c r="K18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
         <v>92</v>
       </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
         <v>93</v>
       </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="K19" t="s">
         <v>94</v>
-      </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" t="s">
-        <v>95</v>
-      </c>
-      <c r="K19" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K20" t="s">
         <v>98</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" t="s">
-        <v>95</v>
-      </c>
-      <c r="K20" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
         <v>102</v>
       </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" t="s">
         <v>103</v>
       </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="K21" t="s">
         <v>104</v>
-      </c>
-      <c r="F21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
         <v>108</v>
       </c>
-      <c r="B22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" t="s">
         <v>109</v>
       </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>110</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
         <v>111</v>
       </c>
-      <c r="G22" t="s">
+      <c r="K22" t="s">
         <v>112</v>
-      </c>
-      <c r="H22" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" t="s">
-        <v>113</v>
-      </c>
-      <c r="K22" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
         <v>119</v>
       </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" t="s">
         <v>120</v>
       </c>
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>121</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s">
         <v>122</v>
       </c>
-      <c r="G23" t="s">
+      <c r="K23" t="s">
         <v>123</v>
-      </c>
-      <c r="H23" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" t="s">
-        <v>124</v>
-      </c>
-      <c r="K23" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
         <v>129</v>
       </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" t="s">
         <v>130</v>
       </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>131</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s">
         <v>132</v>
       </c>
-      <c r="G24" t="s">
+      <c r="K24" t="s">
         <v>133</v>
-      </c>
-      <c r="H24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K24" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" t="s">
         <v>136</v>
       </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" t="s">
         <v>137</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>138</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>139</v>
       </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s">
         <v>140</v>
       </c>
-      <c r="G25" t="s">
+      <c r="K25" t="s">
         <v>141</v>
-      </c>
-      <c r="H25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" t="s">
-        <v>142</v>
-      </c>
-      <c r="K25" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
         <v>146</v>
       </c>
-      <c r="B26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" t="s">
         <v>147</v>
       </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>148</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s">
         <v>149</v>
       </c>
-      <c r="G26" t="s">
+      <c r="K26" t="s">
         <v>150</v>
-      </c>
-      <c r="H26" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" t="s">
-        <v>151</v>
-      </c>
-      <c r="K26" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" t="s">
         <v>156</v>
       </c>
-      <c r="B27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" t="s">
         <v>157</v>
       </c>
-      <c r="D27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>158</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H27" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" t="s">
         <v>159</v>
       </c>
-      <c r="G27" t="s">
+      <c r="J27" t="s">
+        <v>111</v>
+      </c>
+      <c r="K27" t="s">
         <v>160</v>
-      </c>
-      <c r="H27" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" t="s">
-        <v>161</v>
-      </c>
-      <c r="J27" t="s">
-        <v>113</v>
-      </c>
-      <c r="K27" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" t="s">
         <v>164</v>
       </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="F28" t="s">
         <v>165</v>
       </c>
-      <c r="D28" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>166</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" t="s">
+        <v>159</v>
+      </c>
+      <c r="J28" t="s">
         <v>167</v>
       </c>
-      <c r="G28" t="s">
+      <c r="K28" t="s">
         <v>168</v>
-      </c>
-      <c r="H28" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" t="s">
-        <v>161</v>
-      </c>
-      <c r="J28" t="s">
-        <v>169</v>
-      </c>
-      <c r="K28" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" t="s">
         <v>172</v>
       </c>
-      <c r="B29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" t="s">
         <v>173</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>174</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>175</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s">
         <v>176</v>
       </c>
-      <c r="G29" t="s">
+      <c r="K29" t="s">
         <v>177</v>
-      </c>
-      <c r="H29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" t="s">
-        <v>178</v>
-      </c>
-      <c r="K29" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
         <v>181</v>
       </c>
-      <c r="B30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="G30" t="s">
         <v>182</v>
       </c>
-      <c r="D30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" t="s">
         <v>183</v>
       </c>
-      <c r="G30" t="s">
+      <c r="J30" t="s">
         <v>184</v>
       </c>
-      <c r="H30" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="K30" t="s">
         <v>185</v>
-      </c>
-      <c r="J30" t="s">
-        <v>186</v>
-      </c>
-      <c r="K30" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" t="s">
         <v>188</v>
       </c>
-      <c r="B31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
         <v>189</v>
       </c>
-      <c r="D31" t="s">
+      <c r="G31" t="s">
         <v>190</v>
       </c>
-      <c r="E31" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" t="s">
         <v>191</v>
       </c>
-      <c r="G31" t="s">
+      <c r="K31" t="s">
         <v>192</v>
-      </c>
-      <c r="H31" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" t="s">
-        <v>193</v>
-      </c>
-      <c r="K31" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" t="s">
         <v>195</v>
       </c>
-      <c r="B32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="F32" t="s">
         <v>196</v>
       </c>
-      <c r="D32" t="s">
-        <v>190</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
+        <v>196</v>
+      </c>
+      <c r="H32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" t="s">
         <v>197</v>
-      </c>
-      <c r="F32" t="s">
-        <v>198</v>
-      </c>
-      <c r="G32" t="s">
-        <v>198</v>
-      </c>
-      <c r="H32" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" t="s">
-        <v>193</v>
-      </c>
-      <c r="K32" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H33" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" t="s">
+        <v>191</v>
+      </c>
+      <c r="K33" t="s">
         <v>200</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E33" t="s">
-        <v>197</v>
-      </c>
-      <c r="F33" t="s">
-        <v>198</v>
-      </c>
-      <c r="G33" t="s">
-        <v>198</v>
-      </c>
-      <c r="H33" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" t="s">
-        <v>193</v>
-      </c>
-      <c r="K33" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" t="s">
         <v>203</v>
       </c>
-      <c r="B34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="F34" t="s">
         <v>204</v>
       </c>
-      <c r="D34" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>205</v>
       </c>
-      <c r="F34" t="s">
+      <c r="H34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" t="s">
+        <v>159</v>
+      </c>
+      <c r="J34" t="s">
         <v>206</v>
       </c>
-      <c r="G34" t="s">
+      <c r="K34" t="s">
         <v>207</v>
-      </c>
-      <c r="H34" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" t="s">
-        <v>161</v>
-      </c>
-      <c r="J34" t="s">
-        <v>208</v>
-      </c>
-      <c r="K34" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" t="s">
         <v>210</v>
       </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="F35" t="s">
         <v>211</v>
       </c>
-      <c r="D35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>212</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" t="s">
         <v>213</v>
       </c>
-      <c r="G35" t="s">
+      <c r="K35" t="s">
         <v>214</v>
-      </c>
-      <c r="H35" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" t="s">
-        <v>215</v>
-      </c>
-      <c r="K35" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" t="s">
         <v>220</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>221</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>222</v>
       </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
         <v>223</v>
       </c>
-      <c r="G36" t="s">
+      <c r="K36" t="s">
         <v>224</v>
-      </c>
-      <c r="H36" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" t="s">
-        <v>225</v>
-      </c>
-      <c r="K36" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" t="s">
         <v>221</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>222</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s">
         <v>223</v>
       </c>
-      <c r="G37" t="s">
-        <v>224</v>
-      </c>
-      <c r="H37" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" t="s">
-        <v>225</v>
-      </c>
       <c r="K37" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D38" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" t="s">
         <v>221</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>222</v>
       </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
         <v>223</v>
       </c>
-      <c r="G38" t="s">
-        <v>224</v>
-      </c>
-      <c r="H38" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" t="s">
-        <v>225</v>
-      </c>
       <c r="K38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" t="s">
         <v>109</v>
       </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>110</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
         <v>111</v>
       </c>
-      <c r="G39" t="s">
+      <c r="K39" t="s">
         <v>112</v>
-      </c>
-      <c r="H39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" t="s">
-        <v>113</v>
-      </c>
-      <c r="K39" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" t="s">
         <v>120</v>
       </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>121</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s">
         <v>122</v>
       </c>
-      <c r="G40" t="s">
+      <c r="K40" t="s">
         <v>123</v>
-      </c>
-      <c r="H40" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" t="s">
-        <v>124</v>
-      </c>
-      <c r="K40" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" t="s">
         <v>147</v>
       </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="G41" t="s">
         <v>148</v>
       </c>
-      <c r="F41" t="s">
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" t="s">
         <v>149</v>
       </c>
-      <c r="G41" t="s">
+      <c r="K41" t="s">
         <v>150</v>
-      </c>
-      <c r="H41" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" t="s">
-        <v>151</v>
-      </c>
-      <c r="K41" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" t="s">
+        <v>219</v>
+      </c>
+      <c r="E42" t="s">
         <v>220</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>221</v>
       </c>
-      <c r="E42" t="s">
+      <c r="G42" t="s">
         <v>222</v>
       </c>
-      <c r="F42" t="s">
+      <c r="H42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" t="s">
         <v>223</v>
       </c>
-      <c r="G42" t="s">
+      <c r="K42" t="s">
         <v>224</v>
-      </c>
-      <c r="H42" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" t="s">
-        <v>225</v>
-      </c>
-      <c r="K42" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" t="s">
+        <v>220</v>
+      </c>
+      <c r="F43" t="s">
         <v>221</v>
       </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>222</v>
       </c>
-      <c r="F43" t="s">
+      <c r="H43" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" t="s">
         <v>223</v>
       </c>
-      <c r="G43" t="s">
-        <v>224</v>
-      </c>
-      <c r="H43" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" t="s">
-        <v>19</v>
-      </c>
-      <c r="J43" t="s">
-        <v>225</v>
-      </c>
       <c r="K43" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D44" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" t="s">
+        <v>220</v>
+      </c>
+      <c r="F44" t="s">
         <v>221</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>222</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" t="s">
         <v>223</v>
       </c>
-      <c r="G44" t="s">
-        <v>224</v>
-      </c>
-      <c r="H44" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" t="s">
-        <v>225</v>
-      </c>
       <c r="K44" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B45" t="s">
+      <c r="D45" t="s">
         <v>219</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="E45" t="s">
         <v>220</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>221</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>222</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" t="s">
         <v>223</v>
       </c>
-      <c r="G45" t="s">
+      <c r="K45" t="s">
         <v>224</v>
-      </c>
-      <c r="H45" t="s">
-        <v>28</v>
-      </c>
-      <c r="I45" t="s">
-        <v>19</v>
-      </c>
-      <c r="J45" t="s">
-        <v>225</v>
-      </c>
-      <c r="K45" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" t="s">
+        <v>217</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D46" t="s">
+        <v>219</v>
+      </c>
+      <c r="E46" t="s">
+        <v>220</v>
+      </c>
+      <c r="F46" t="s">
+        <v>221</v>
+      </c>
+      <c r="G46" t="s">
+        <v>222</v>
+      </c>
+      <c r="H46" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" t="s">
+        <v>223</v>
+      </c>
+      <c r="K46" t="s">
         <v>230</v>
-      </c>
-      <c r="B46" t="s">
-        <v>219</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D46" t="s">
-        <v>221</v>
-      </c>
-      <c r="E46" t="s">
-        <v>222</v>
-      </c>
-      <c r="F46" t="s">
-        <v>223</v>
-      </c>
-      <c r="G46" t="s">
-        <v>224</v>
-      </c>
-      <c r="H46" t="s">
-        <v>28</v>
-      </c>
-      <c r="I46" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" t="s">
-        <v>225</v>
-      </c>
-      <c r="K46" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" t="s">
         <v>45</v>
       </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="K47" t="s">
         <v>46</v>
-      </c>
-      <c r="F47" t="s">
-        <v>34</v>
-      </c>
-      <c r="G47" t="s">
-        <v>34</v>
-      </c>
-      <c r="H47" t="s">
-        <v>18</v>
-      </c>
-      <c r="I47" t="s">
-        <v>35</v>
-      </c>
-      <c r="J47" t="s">
-        <v>47</v>
-      </c>
-      <c r="K47" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" t="s">
         <v>69</v>
       </c>
-      <c r="D48" t="s">
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" t="s">
         <v>70</v>
       </c>
-      <c r="E48" t="s">
+      <c r="K48" t="s">
         <v>71</v>
-      </c>
-      <c r="F48" t="s">
-        <v>34</v>
-      </c>
-      <c r="G48" t="s">
-        <v>34</v>
-      </c>
-      <c r="H48" t="s">
-        <v>18</v>
-      </c>
-      <c r="I48" t="s">
-        <v>35</v>
-      </c>
-      <c r="J48" t="s">
-        <v>72</v>
-      </c>
-      <c r="K48" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" t="s">
         <v>76</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" t="s">
         <v>77</v>
-      </c>
-      <c r="E49" t="s">
-        <v>78</v>
-      </c>
-      <c r="F49" t="s">
-        <v>34</v>
-      </c>
-      <c r="G49" t="s">
-        <v>34</v>
-      </c>
-      <c r="H49" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" t="s">
-        <v>35</v>
-      </c>
-      <c r="J49" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
         <v>93</v>
       </c>
-      <c r="D50" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="K50" t="s">
         <v>94</v>
-      </c>
-      <c r="F50" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50" t="s">
-        <v>34</v>
-      </c>
-      <c r="H50" t="s">
-        <v>28</v>
-      </c>
-      <c r="I50" t="s">
-        <v>19</v>
-      </c>
-      <c r="J50" t="s">
-        <v>95</v>
-      </c>
-      <c r="K50" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" t="s">
+        <v>93</v>
+      </c>
+      <c r="K51" t="s">
         <v>94</v>
-      </c>
-      <c r="F51" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51" t="s">
-        <v>34</v>
-      </c>
-      <c r="H51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I51" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51" t="s">
-        <v>95</v>
-      </c>
-      <c r="K51" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>102</v>
+      </c>
+      <c r="F52" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H52" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" t="s">
         <v>103</v>
       </c>
-      <c r="D52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="K52" t="s">
         <v>104</v>
-      </c>
-      <c r="F52" t="s">
-        <v>34</v>
-      </c>
-      <c r="G52" t="s">
-        <v>34</v>
-      </c>
-      <c r="H52" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" t="s">
-        <v>35</v>
-      </c>
-      <c r="J52" t="s">
-        <v>105</v>
-      </c>
-      <c r="K52" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" t="s">
         <v>109</v>
       </c>
-      <c r="D53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>110</v>
       </c>
-      <c r="F53" t="s">
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" t="s">
         <v>111</v>
       </c>
-      <c r="G53" t="s">
+      <c r="K53" t="s">
         <v>112</v>
-      </c>
-      <c r="H53" t="s">
-        <v>18</v>
-      </c>
-      <c r="I53" t="s">
-        <v>19</v>
-      </c>
-      <c r="J53" t="s">
-        <v>113</v>
-      </c>
-      <c r="K53" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>119</v>
+      </c>
+      <c r="F54" t="s">
         <v>120</v>
       </c>
-      <c r="D54" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>121</v>
       </c>
-      <c r="F54" t="s">
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" t="s">
         <v>122</v>
       </c>
-      <c r="G54" t="s">
+      <c r="K54" t="s">
         <v>123</v>
-      </c>
-      <c r="H54" t="s">
-        <v>18</v>
-      </c>
-      <c r="I54" t="s">
-        <v>19</v>
-      </c>
-      <c r="J54" t="s">
-        <v>124</v>
-      </c>
-      <c r="K54" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F55" t="s">
+        <v>138</v>
+      </c>
+      <c r="G55" t="s">
+        <v>139</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" t="s">
         <v>140</v>
       </c>
-      <c r="G55" t="s">
+      <c r="K55" t="s">
         <v>141</v>
-      </c>
-      <c r="H55" t="s">
-        <v>18</v>
-      </c>
-      <c r="I55" t="s">
-        <v>19</v>
-      </c>
-      <c r="J55" t="s">
-        <v>142</v>
-      </c>
-      <c r="K55" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" t="s">
         <v>147</v>
       </c>
-      <c r="D56" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>148</v>
       </c>
-      <c r="F56" t="s">
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" t="s">
         <v>149</v>
       </c>
-      <c r="G56" t="s">
+      <c r="K56" t="s">
         <v>150</v>
-      </c>
-      <c r="H56" t="s">
-        <v>18</v>
-      </c>
-      <c r="I56" t="s">
-        <v>19</v>
-      </c>
-      <c r="J56" t="s">
-        <v>151</v>
-      </c>
-      <c r="K56" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" t="s">
+        <v>156</v>
+      </c>
+      <c r="F57" t="s">
         <v>157</v>
       </c>
-      <c r="D57" t="s">
-        <v>138</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>158</v>
       </c>
-      <c r="F57" t="s">
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" t="s">
         <v>159</v>
       </c>
-      <c r="G57" t="s">
+      <c r="J57" t="s">
+        <v>111</v>
+      </c>
+      <c r="K57" t="s">
         <v>160</v>
-      </c>
-      <c r="H57" t="s">
-        <v>28</v>
-      </c>
-      <c r="I57" t="s">
-        <v>161</v>
-      </c>
-      <c r="J57" t="s">
-        <v>113</v>
-      </c>
-      <c r="K57" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" t="s">
+        <v>164</v>
+      </c>
+      <c r="F58" t="s">
         <v>165</v>
       </c>
-      <c r="D58" t="s">
-        <v>138</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>166</v>
       </c>
-      <c r="F58" t="s">
+      <c r="H58" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58" t="s">
+        <v>159</v>
+      </c>
+      <c r="J58" t="s">
         <v>167</v>
       </c>
-      <c r="G58" t="s">
+      <c r="K58" t="s">
         <v>168</v>
-      </c>
-      <c r="H58" t="s">
-        <v>28</v>
-      </c>
-      <c r="I58" t="s">
-        <v>161</v>
-      </c>
-      <c r="J58" t="s">
-        <v>169</v>
-      </c>
-      <c r="K58" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" t="s">
+        <v>172</v>
+      </c>
+      <c r="E59" t="s">
         <v>173</v>
       </c>
-      <c r="D59" t="s">
+      <c r="F59" t="s">
         <v>174</v>
       </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>175</v>
       </c>
-      <c r="F59" t="s">
+      <c r="H59" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" t="s">
         <v>176</v>
       </c>
-      <c r="G59" t="s">
+      <c r="K59" t="s">
         <v>177</v>
-      </c>
-      <c r="H59" t="s">
-        <v>28</v>
-      </c>
-      <c r="I59" t="s">
-        <v>19</v>
-      </c>
-      <c r="J59" t="s">
-        <v>178</v>
-      </c>
-      <c r="K59" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" t="s">
         <v>211</v>
       </c>
-      <c r="D60" t="s">
-        <v>138</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>212</v>
       </c>
-      <c r="F60" t="s">
+      <c r="H60" t="s">
+        <v>26</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" t="s">
         <v>213</v>
       </c>
-      <c r="G60" t="s">
+      <c r="K60" t="s">
         <v>214</v>
-      </c>
-      <c r="H60" t="s">
-        <v>28</v>
-      </c>
-      <c r="I60" t="s">
-        <v>19</v>
-      </c>
-      <c r="J60" t="s">
-        <v>215</v>
-      </c>
-      <c r="K60" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C61" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D61" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61" t="s">
         <v>220</v>
       </c>
-      <c r="D61" t="s">
+      <c r="F61" t="s">
         <v>221</v>
       </c>
-      <c r="E61" t="s">
+      <c r="G61" t="s">
         <v>222</v>
       </c>
-      <c r="F61" t="s">
+      <c r="H61" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" t="s">
         <v>223</v>
       </c>
-      <c r="G61" t="s">
+      <c r="K61" t="s">
         <v>224</v>
-      </c>
-      <c r="H61" t="s">
-        <v>28</v>
-      </c>
-      <c r="I61" t="s">
-        <v>19</v>
-      </c>
-      <c r="J61" t="s">
-        <v>225</v>
-      </c>
-      <c r="K61" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D62" t="s">
+        <v>219</v>
+      </c>
+      <c r="E62" t="s">
+        <v>220</v>
+      </c>
+      <c r="F62" t="s">
         <v>221</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>222</v>
       </c>
-      <c r="F62" t="s">
+      <c r="H62" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" t="s">
         <v>223</v>
       </c>
-      <c r="G62" t="s">
-        <v>224</v>
-      </c>
-      <c r="H62" t="s">
-        <v>28</v>
-      </c>
-      <c r="I62" t="s">
-        <v>19</v>
-      </c>
-      <c r="J62" t="s">
-        <v>225</v>
-      </c>
       <c r="K62" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D63" t="s">
+        <v>219</v>
+      </c>
+      <c r="E63" t="s">
+        <v>220</v>
+      </c>
+      <c r="F63" t="s">
         <v>221</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>222</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" t="s">
         <v>223</v>
       </c>
-      <c r="G63" t="s">
-        <v>224</v>
-      </c>
-      <c r="H63" t="s">
-        <v>28</v>
-      </c>
-      <c r="I63" t="s">
-        <v>19</v>
-      </c>
-      <c r="J63" t="s">
-        <v>225</v>
-      </c>
       <c r="K63" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -3362,34 +3364,34 @@
         <v>101</v>
       </c>
       <c r="B64" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>108</v>
+      </c>
+      <c r="F64" t="s">
         <v>109</v>
       </c>
-      <c r="D64" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="G64" t="s">
         <v>110</v>
       </c>
-      <c r="F64" t="s">
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" t="s">
         <v>111</v>
       </c>
-      <c r="G64" t="s">
+      <c r="K64" t="s">
         <v>112</v>
-      </c>
-      <c r="H64" t="s">
-        <v>18</v>
-      </c>
-      <c r="I64" t="s">
-        <v>19</v>
-      </c>
-      <c r="J64" t="s">
-        <v>113</v>
-      </c>
-      <c r="K64" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
@@ -3397,34 +3399,34 @@
         <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" t="s">
+        <v>136</v>
+      </c>
+      <c r="E65" t="s">
         <v>137</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
         <v>138</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>139</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" t="s">
         <v>140</v>
       </c>
-      <c r="G65" t="s">
+      <c r="K65" t="s">
         <v>141</v>
-      </c>
-      <c r="H65" t="s">
-        <v>18</v>
-      </c>
-      <c r="I65" t="s">
-        <v>19</v>
-      </c>
-      <c r="J65" t="s">
-        <v>142</v>
-      </c>
-      <c r="K65" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
@@ -3432,25 +3434,25 @@
         <v>103</v>
       </c>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C66" s="2">
         <v>760</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J66" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
@@ -3458,34 +3460,34 @@
         <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C67" s="2">
         <v>948</v>
       </c>
       <c r="D67" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E67" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F67" s="5" t="s">
-        <v>249</v>
-      </c>
       <c r="G67" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H67" t="s">
+        <v>26</v>
+      </c>
+      <c r="I67" t="s">
+        <v>159</v>
+      </c>
+      <c r="J67" t="s">
+        <v>244</v>
+      </c>
+      <c r="K67" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="H67" t="s">
-        <v>28</v>
-      </c>
-      <c r="I67" t="s">
-        <v>161</v>
-      </c>
-      <c r="J67" t="s">
-        <v>246</v>
-      </c>
-      <c r="K67" s="5" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
@@ -3493,34 +3495,34 @@
         <v>105</v>
       </c>
       <c r="B68" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E68" t="s">
+        <v>210</v>
+      </c>
+      <c r="F68" t="s">
+        <v>211</v>
+      </c>
+      <c r="G68" t="s">
         <v>212</v>
       </c>
-      <c r="F68" t="s">
+      <c r="H68" t="s">
+        <v>26</v>
+      </c>
+      <c r="I68" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" t="s">
         <v>213</v>
       </c>
-      <c r="G68" t="s">
+      <c r="K68" t="s">
         <v>214</v>
-      </c>
-      <c r="H68" t="s">
-        <v>28</v>
-      </c>
-      <c r="I68" t="s">
-        <v>19</v>
-      </c>
-      <c r="J68" t="s">
-        <v>215</v>
-      </c>
-      <c r="K68" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
@@ -3528,34 +3530,34 @@
         <v>106</v>
       </c>
       <c r="B69" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E69" t="s">
+        <v>220</v>
+      </c>
+      <c r="F69" t="s">
+        <v>221</v>
+      </c>
+      <c r="G69" t="s">
         <v>222</v>
       </c>
-      <c r="F69" t="s">
+      <c r="H69" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" t="s">
         <v>223</v>
       </c>
-      <c r="G69" t="s">
+      <c r="K69" t="s">
         <v>224</v>
-      </c>
-      <c r="H69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I69" t="s">
-        <v>19</v>
-      </c>
-      <c r="J69" t="s">
-        <v>225</v>
-      </c>
-      <c r="K69" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
@@ -3563,34 +3565,34 @@
         <v>107</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>244</v>
-      </c>
       <c r="E70" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F70" t="s">
+        <v>181</v>
+      </c>
+      <c r="G70" t="s">
+        <v>182</v>
+      </c>
+      <c r="H70" t="s">
+        <v>26</v>
+      </c>
+      <c r="I70" t="s">
         <v>183</v>
       </c>
-      <c r="G70" t="s">
+      <c r="J70" t="s">
         <v>184</v>
       </c>
-      <c r="H70" t="s">
-        <v>28</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>185</v>
-      </c>
-      <c r="J70" t="s">
-        <v>186</v>
-      </c>
-      <c r="K70" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -3598,34 +3600,34 @@
         <v>108</v>
       </c>
       <c r="B71" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E71" t="s">
+        <v>156</v>
+      </c>
+      <c r="F71" t="s">
+        <v>157</v>
+      </c>
+      <c r="G71" t="s">
         <v>158</v>
       </c>
-      <c r="F71" t="s">
+      <c r="H71" t="s">
+        <v>26</v>
+      </c>
+      <c r="I71" t="s">
         <v>159</v>
       </c>
-      <c r="G71" t="s">
+      <c r="J71" t="s">
+        <v>111</v>
+      </c>
+      <c r="K71" t="s">
         <v>160</v>
-      </c>
-      <c r="H71" t="s">
-        <v>28</v>
-      </c>
-      <c r="I71" t="s">
-        <v>161</v>
-      </c>
-      <c r="J71" t="s">
-        <v>113</v>
-      </c>
-      <c r="K71" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-1301-Bus.xlsx
+++ b/db/A7XLK-1301-Bus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E95109-59CC-F14A-81B1-5D03BE06EEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7E607E-5DF0-1D42-9B7C-5EDD7A1EBB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1940" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="257">
   <si>
     <t>No</t>
   </si>
@@ -816,6 +816,10 @@
   </si>
   <si>
     <t>https://ebus.tycg.gov.tw/ebus/driving-map/711</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.tycg.gov.tw/ebus/driving-map/65331</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1413,42 +1417,45 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>243</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>243</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>33</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -1457,36 +1464,36 @@
         <v>242</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>243</v>
-      </c>
-      <c r="H8" t="s">
-        <v>243</v>
+        <v>36</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -1495,36 +1502,36 @@
         <v>242</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>244</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -1533,19 +1540,19 @@
         <v>242</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
@@ -1553,16 +1560,16 @@
       <c r="J10" t="s">
         <v>32</v>
       </c>
-      <c r="K10" t="s">
-        <v>44</v>
+      <c r="K10" s="1">
+        <v>0.69791666666666696</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -1571,19 +1578,19 @@
         <v>242</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
         <v>43</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -1592,15 +1599,15 @@
         <v>32</v>
       </c>
       <c r="K11" s="1">
-        <v>0.69791666666666696</v>
+        <v>0.30555555555555602</v>
       </c>
       <c r="L11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -1609,19 +1616,19 @@
         <v>242</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -1629,16 +1636,16 @@
       <c r="J12" t="s">
         <v>32</v>
       </c>
-      <c r="K12" s="1">
-        <v>0.30555555555555602</v>
+      <c r="K12" t="s">
+        <v>58</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -1647,36 +1654,33 @@
         <v>242</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
         <v>32</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
-      </c>
-      <c r="L13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -1685,33 +1689,36 @@
         <v>242</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="L14" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -1720,19 +1727,19 @@
         <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
@@ -1741,15 +1748,15 @@
         <v>70</v>
       </c>
       <c r="K15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -1758,36 +1765,36 @@
         <v>242</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="K16" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L16" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -1796,7 +1803,7 @@
         <v>242</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
         <v>56</v>
@@ -1805,10 +1812,10 @@
         <v>80</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
@@ -1820,12 +1827,12 @@
         <v>81</v>
       </c>
       <c r="L17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -1834,74 +1841,74 @@
         <v>242</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="L18" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>255</v>
+        <v>96</v>
+      </c>
+      <c r="G19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" t="s">
+        <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="L19" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -1910,19 +1917,19 @@
         <v>240</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G20" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H20" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="I20" t="s">
         <v>16</v>
@@ -1931,15 +1938,15 @@
         <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="L20" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -1948,19 +1955,19 @@
         <v>240</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I21" t="s">
         <v>16</v>
@@ -1969,15 +1976,15 @@
         <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L21" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -1986,19 +1993,19 @@
         <v>240</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G22" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I22" t="s">
         <v>16</v>
@@ -2007,15 +2014,15 @@
         <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L22" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -2024,19 +2031,19 @@
         <v>240</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G23" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I23" t="s">
         <v>16</v>
@@ -2045,53 +2052,53 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="K24" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="L24" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -2100,19 +2107,19 @@
         <v>241</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
         <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G25" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H25" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2121,15 +2128,15 @@
         <v>147</v>
       </c>
       <c r="K25" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -2138,36 +2145,36 @@
         <v>241</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="F26" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G26" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="H26" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I26" t="s">
         <v>26</v>
       </c>
       <c r="J26" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -2176,36 +2183,36 @@
         <v>241</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E27" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s">
         <v>161</v>
       </c>
       <c r="G27" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H27" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I27" t="s">
         <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="L27" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -2214,36 +2221,36 @@
         <v>241</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="F28" t="s">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H28" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>171</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -2252,19 +2259,19 @@
         <v>241</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
         <v>176</v>
       </c>
       <c r="F29" t="s">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="G29" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H29" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="I29" t="s">
         <v>26</v>
@@ -2276,12 +2283,12 @@
         <v>179</v>
       </c>
       <c r="L29" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -2290,7 +2297,7 @@
         <v>241</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E30" t="s">
         <v>176</v>
@@ -2314,12 +2321,12 @@
         <v>179</v>
       </c>
       <c r="L30" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -2328,36 +2335,36 @@
         <v>241</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E31" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G31" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H31" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="K31" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="L31" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -2366,36 +2373,36 @@
         <v>241</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E32" t="s">
         <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G32" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H32" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="L32" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -2404,19 +2411,19 @@
         <v>241</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="F33" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G33" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H33" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
@@ -2425,15 +2432,15 @@
         <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L33" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -2442,7 +2449,7 @@
         <v>241</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E34" t="s">
         <v>207</v>
@@ -2466,12 +2473,12 @@
         <v>211</v>
       </c>
       <c r="L34" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -2480,7 +2487,7 @@
         <v>241</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E35" t="s">
         <v>207</v>
@@ -2509,7 +2516,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>222</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -2518,31 +2525,28 @@
         <v>241</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>207</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>208</v>
-      </c>
-      <c r="G36" t="s">
-        <v>209</v>
-      </c>
-      <c r="H36" t="s">
-        <v>210</v>
+        <v>13</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>256</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J36" t="s">
         <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>211</v>
-      </c>
-      <c r="L36" t="s">
-        <v>218</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -3659,34 +3663,36 @@
     <hyperlink ref="L64" r:id="rId1" xr:uid="{9879FFAF-1B89-4142-BC32-5F8FF16D1C65}"/>
     <hyperlink ref="H64" r:id="rId2" xr:uid="{03C06EE7-B036-FD43-BE6D-03B1D0965FA4}"/>
     <hyperlink ref="G64" r:id="rId3" xr:uid="{D816E695-43E8-B848-8865-24DFCE3DDE79}"/>
-    <hyperlink ref="H9" r:id="rId4" xr:uid="{B38EF02A-B2AF-7C45-90B3-3FDB0455F17E}"/>
-    <hyperlink ref="H10" r:id="rId5" xr:uid="{A1583536-1BB0-FB4F-B69B-5D53DFD19104}"/>
-    <hyperlink ref="H11" r:id="rId6" xr:uid="{600C9A84-F812-0E4F-BA2A-4CA0F3FE615C}"/>
-    <hyperlink ref="H12" r:id="rId7" xr:uid="{61C1C9BB-BA75-1F46-BF63-C986010EC06F}"/>
-    <hyperlink ref="H13" r:id="rId8" xr:uid="{F45F7B93-8634-034E-9C7E-E3DD87128229}"/>
-    <hyperlink ref="H14" r:id="rId9" xr:uid="{E62B9FDC-87D7-9B46-B497-3086B58C18C3}"/>
-    <hyperlink ref="H15" r:id="rId10" xr:uid="{31A5AAD2-57C4-9841-9B92-3613E367BF9D}"/>
-    <hyperlink ref="H16" r:id="rId11" xr:uid="{5343F1A6-B31A-C247-9064-9380FF431AB0}"/>
-    <hyperlink ref="H17" r:id="rId12" xr:uid="{F2628EE4-27D6-B04B-B7BB-A86B72067AAD}"/>
-    <hyperlink ref="H19" r:id="rId13" xr:uid="{B50369B8-AA2F-4547-B593-6205CEA577F1}"/>
+    <hyperlink ref="H8" r:id="rId4" xr:uid="{B38EF02A-B2AF-7C45-90B3-3FDB0455F17E}"/>
+    <hyperlink ref="H9" r:id="rId5" xr:uid="{A1583536-1BB0-FB4F-B69B-5D53DFD19104}"/>
+    <hyperlink ref="H10" r:id="rId6" xr:uid="{600C9A84-F812-0E4F-BA2A-4CA0F3FE615C}"/>
+    <hyperlink ref="H11" r:id="rId7" xr:uid="{61C1C9BB-BA75-1F46-BF63-C986010EC06F}"/>
+    <hyperlink ref="H12" r:id="rId8" xr:uid="{F45F7B93-8634-034E-9C7E-E3DD87128229}"/>
+    <hyperlink ref="H13" r:id="rId9" xr:uid="{E62B9FDC-87D7-9B46-B497-3086B58C18C3}"/>
+    <hyperlink ref="H14" r:id="rId10" xr:uid="{31A5AAD2-57C4-9841-9B92-3613E367BF9D}"/>
+    <hyperlink ref="H15" r:id="rId11" xr:uid="{5343F1A6-B31A-C247-9064-9380FF431AB0}"/>
+    <hyperlink ref="H16" r:id="rId12" xr:uid="{F2628EE4-27D6-B04B-B7BB-A86B72067AAD}"/>
+    <hyperlink ref="H18" r:id="rId13" xr:uid="{B50369B8-AA2F-4547-B593-6205CEA577F1}"/>
     <hyperlink ref="H45" r:id="rId14" xr:uid="{54D5D8F7-54E0-104B-95A4-9D5684440C2A}"/>
     <hyperlink ref="H46" r:id="rId15" xr:uid="{D517414B-9453-4846-A2C4-6008C25A6E81}"/>
     <hyperlink ref="H47" r:id="rId16" xr:uid="{4DC9BDDF-C26B-F54B-9352-F94D3940FB1F}"/>
     <hyperlink ref="H49" r:id="rId17" xr:uid="{244B43CA-BC03-8449-AB34-832F2A4A08A6}"/>
-    <hyperlink ref="G9" r:id="rId18" xr:uid="{87BCA5E7-61AE-9343-AFBF-4949F97A1573}"/>
-    <hyperlink ref="G10" r:id="rId19" xr:uid="{EDA56214-229D-AA44-9531-B2C732F1EBFB}"/>
-    <hyperlink ref="G11" r:id="rId20" xr:uid="{1115C12E-C2EF-2D44-8331-D9F21E5FAB8B}"/>
-    <hyperlink ref="G12" r:id="rId21" xr:uid="{BE0D18CF-8989-F440-BB14-41637E2C3090}"/>
-    <hyperlink ref="G13" r:id="rId22" xr:uid="{D6BC3C80-A3EB-BB4F-BEB4-F3B6E5C92EBC}"/>
-    <hyperlink ref="G14" r:id="rId23" xr:uid="{B7CC6FE9-BB6B-8440-90D6-8AF24B1FAAE2}"/>
-    <hyperlink ref="G15" r:id="rId24" xr:uid="{A2FF1CD3-1F4F-D14C-AEBB-EE7B5C78C33B}"/>
-    <hyperlink ref="G16" r:id="rId25" xr:uid="{56D0F2CF-E77D-1E4A-B084-D982FF9FB4DD}"/>
-    <hyperlink ref="G17" r:id="rId26" xr:uid="{A22E894A-9D67-2E4E-99E8-D4A7734F9214}"/>
-    <hyperlink ref="G19" r:id="rId27" xr:uid="{219E7006-8AD1-1440-9D44-8E7CBA1935DC}"/>
+    <hyperlink ref="G8" r:id="rId18" xr:uid="{87BCA5E7-61AE-9343-AFBF-4949F97A1573}"/>
+    <hyperlink ref="G9" r:id="rId19" xr:uid="{EDA56214-229D-AA44-9531-B2C732F1EBFB}"/>
+    <hyperlink ref="G10" r:id="rId20" xr:uid="{1115C12E-C2EF-2D44-8331-D9F21E5FAB8B}"/>
+    <hyperlink ref="G11" r:id="rId21" xr:uid="{BE0D18CF-8989-F440-BB14-41637E2C3090}"/>
+    <hyperlink ref="G12" r:id="rId22" xr:uid="{D6BC3C80-A3EB-BB4F-BEB4-F3B6E5C92EBC}"/>
+    <hyperlink ref="G13" r:id="rId23" xr:uid="{B7CC6FE9-BB6B-8440-90D6-8AF24B1FAAE2}"/>
+    <hyperlink ref="G14" r:id="rId24" xr:uid="{A2FF1CD3-1F4F-D14C-AEBB-EE7B5C78C33B}"/>
+    <hyperlink ref="G15" r:id="rId25" xr:uid="{56D0F2CF-E77D-1E4A-B084-D982FF9FB4DD}"/>
+    <hyperlink ref="G16" r:id="rId26" xr:uid="{A22E894A-9D67-2E4E-99E8-D4A7734F9214}"/>
+    <hyperlink ref="G18" r:id="rId27" xr:uid="{219E7006-8AD1-1440-9D44-8E7CBA1935DC}"/>
     <hyperlink ref="G45" r:id="rId28" xr:uid="{D3B084B0-B7B4-624F-83B7-A14B02B8A44A}"/>
     <hyperlink ref="G46" r:id="rId29" xr:uid="{36C0344C-E3E2-2B4F-AB6C-248C1A361A95}"/>
     <hyperlink ref="G47" r:id="rId30" xr:uid="{57E6CB22-2581-1849-AC3B-78064D4FE2FA}"/>
     <hyperlink ref="G49" r:id="rId31" xr:uid="{11599548-4371-8247-A7FC-AAB26906B525}"/>
+    <hyperlink ref="H36" r:id="rId32" xr:uid="{B4964FA7-8E24-324A-B6C6-E13582B429A9}"/>
+    <hyperlink ref="G36" r:id="rId33" xr:uid="{1EED94F5-6694-824D-85B0-338E29E72824}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1301-Bus.xlsx
+++ b/db/A7XLK-1301-Bus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7E607E-5DF0-1D42-9B7C-5EDD7A1EBB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08663BB9-B552-F648-96F2-8FB1C3DCD310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1940" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,9 +91,6 @@
     <t>1212</t>
   </si>
   <si>
-    <t>三重德林寺（三和路）</t>
-  </si>
-  <si>
     <t>https://www.taiwanbus.tw/DyBus.aspx?Lang=Cht&amp;ID=92#1212#0</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>003</t>
   </si>
   <si>
-    <t>202 先經公西站</t>
-  </si>
-  <si>
     <t>體育大學</t>
   </si>
   <si>
@@ -166,9 +160,6 @@
     <t>5057 A</t>
   </si>
   <si>
-    <t>林口長庚醫院(經體育大學）</t>
-  </si>
-  <si>
     <t>https://ebus.tycg.gov.tw/cms/api/route/50571/map/1397/image</t>
   </si>
   <si>
@@ -176,9 +167,6 @@
   </si>
   <si>
     <t>5057 C</t>
-  </si>
-  <si>
-    <t>林口長庚醫院(經長庚養生村）</t>
   </si>
   <si>
     <t>https://ebus.tycg.gov.tw/cms/api/route/50573/map/1398/image</t>
@@ -820,6 +808,22 @@
   </si>
   <si>
     <t>https://ebus.tycg.gov.tw/ebus/driving-map/65331</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口長庚醫院 經體大</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口長庚醫院 經養生村</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三重德林寺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">202 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1199,7 +1203,7 @@
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.83203125" customWidth="1"/>
     <col min="4" max="4" width="10" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="48.33203125" customWidth="1"/>
     <col min="8" max="8" width="53.33203125" customWidth="1"/>
@@ -1216,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1228,10 +1232,10 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
@@ -1292,45 +1296,45 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -1339,33 +1343,33 @@
         <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -1374,33 +1378,33 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I6" t="s">
         <v>16</v>
@@ -1409,489 +1413,489 @@
         <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
       <c r="G7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I7" t="s">
         <v>16</v>
       </c>
       <c r="J7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" t="s">
         <v>32</v>
-      </c>
-      <c r="K7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I8" t="s">
         <v>16</v>
       </c>
       <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
         <v>37</v>
-      </c>
-      <c r="K8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>253</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I10" t="s">
         <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K10" s="1">
         <v>0.69791666666666696</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>254</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
       </c>
       <c r="J11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K11" s="1">
         <v>0.30555555555555602</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I14" t="s">
         <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
       <c r="K16" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
       </c>
       <c r="K17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s">
         <v>16</v>
@@ -1900,36 +1904,36 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I20" t="s">
         <v>16</v>
@@ -1938,36 +1942,36 @@
         <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
         <v>16</v>
@@ -1976,36 +1980,36 @@
         <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" t="s">
         <v>123</v>
-      </c>
-      <c r="E22" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" t="s">
-        <v>127</v>
       </c>
       <c r="I22" t="s">
         <v>16</v>
@@ -2014,36 +2018,36 @@
         <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L22" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I23" t="s">
         <v>16</v>
@@ -2052,466 +2056,466 @@
         <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" t="s">
+        <v>142</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s">
         <v>143</v>
       </c>
-      <c r="E24" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="K24" t="s">
+        <v>95</v>
+      </c>
+      <c r="L24" t="s">
         <v>144</v>
-      </c>
-      <c r="G24" t="s">
-        <v>145</v>
-      </c>
-      <c r="H24" t="s">
-        <v>146</v>
-      </c>
-      <c r="I24" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" t="s">
-        <v>147</v>
-      </c>
-      <c r="K24" t="s">
-        <v>99</v>
-      </c>
-      <c r="L24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s">
+        <v>148</v>
+      </c>
+      <c r="G25" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" t="s">
+        <v>143</v>
+      </c>
+      <c r="K25" t="s">
         <v>151</v>
       </c>
-      <c r="E25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="L25" t="s">
         <v>152</v>
-      </c>
-      <c r="G25" t="s">
-        <v>153</v>
-      </c>
-      <c r="H25" t="s">
-        <v>154</v>
-      </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" t="s">
-        <v>147</v>
-      </c>
-      <c r="K25" t="s">
-        <v>155</v>
-      </c>
-      <c r="L25" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" t="s">
         <v>159</v>
       </c>
-      <c r="E26" t="s">
+      <c r="I26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" t="s">
         <v>160</v>
       </c>
-      <c r="F26" t="s">
+      <c r="L26" t="s">
         <v>161</v>
-      </c>
-      <c r="G26" t="s">
-        <v>162</v>
-      </c>
-      <c r="H26" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" t="s">
-        <v>164</v>
-      </c>
-      <c r="L26" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E27" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" t="s">
+        <v>157</v>
+      </c>
+      <c r="G27" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" t="s">
+        <v>167</v>
+      </c>
+      <c r="K27" t="s">
         <v>168</v>
       </c>
-      <c r="E27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" t="s">
-        <v>161</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="L27" t="s">
         <v>169</v>
-      </c>
-      <c r="H27" t="s">
-        <v>170</v>
-      </c>
-      <c r="I27" t="s">
-        <v>26</v>
-      </c>
-      <c r="J27" t="s">
-        <v>171</v>
-      </c>
-      <c r="K27" t="s">
-        <v>172</v>
-      </c>
-      <c r="L27" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" t="s">
         <v>175</v>
       </c>
-      <c r="E28" t="s">
+      <c r="L28" t="s">
         <v>176</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" t="s">
-        <v>178</v>
-      </c>
-      <c r="I28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" t="s">
-        <v>179</v>
-      </c>
-      <c r="L28" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F29" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G29" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H29" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L29" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E30" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G30" t="s">
+        <v>180</v>
+      </c>
+      <c r="H30" t="s">
+        <v>180</v>
+      </c>
+      <c r="I30" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" t="s">
+        <v>175</v>
+      </c>
+      <c r="L30" t="s">
         <v>184</v>
-      </c>
-      <c r="H30" t="s">
-        <v>184</v>
-      </c>
-      <c r="I30" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" t="s">
-        <v>179</v>
-      </c>
-      <c r="L30" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" t="s">
+        <v>188</v>
+      </c>
+      <c r="H31" t="s">
+        <v>189</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>143</v>
+      </c>
+      <c r="K31" t="s">
         <v>190</v>
       </c>
-      <c r="E31" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="L31" t="s">
         <v>191</v>
-      </c>
-      <c r="G31" t="s">
-        <v>192</v>
-      </c>
-      <c r="H31" t="s">
-        <v>193</v>
-      </c>
-      <c r="I31" t="s">
-        <v>26</v>
-      </c>
-      <c r="J31" t="s">
-        <v>147</v>
-      </c>
-      <c r="K31" t="s">
-        <v>194</v>
-      </c>
-      <c r="L31" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" t="s">
         <v>197</v>
       </c>
-      <c r="E32" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="L32" t="s">
         <v>198</v>
-      </c>
-      <c r="G32" t="s">
-        <v>199</v>
-      </c>
-      <c r="H32" t="s">
-        <v>200</v>
-      </c>
-      <c r="I32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J32" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" t="s">
-        <v>201</v>
-      </c>
-      <c r="L32" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" t="s">
+        <v>204</v>
+      </c>
+      <c r="G33" t="s">
+        <v>205</v>
+      </c>
+      <c r="H33" t="s">
         <v>206</v>
       </c>
-      <c r="E33" t="s">
+      <c r="I33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" t="s">
         <v>207</v>
       </c>
-      <c r="F33" t="s">
+      <c r="L33" t="s">
         <v>208</v>
-      </c>
-      <c r="G33" t="s">
-        <v>209</v>
-      </c>
-      <c r="H33" t="s">
-        <v>210</v>
-      </c>
-      <c r="I33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" t="s">
-        <v>211</v>
-      </c>
-      <c r="L33" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E34" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" t="s">
+        <v>204</v>
+      </c>
+      <c r="G34" t="s">
+        <v>205</v>
+      </c>
+      <c r="H34" t="s">
+        <v>206</v>
+      </c>
+      <c r="I34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" t="s">
         <v>207</v>
       </c>
-      <c r="F34" t="s">
-        <v>208</v>
-      </c>
-      <c r="G34" t="s">
-        <v>209</v>
-      </c>
-      <c r="H34" t="s">
-        <v>210</v>
-      </c>
-      <c r="I34" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" t="s">
-        <v>211</v>
-      </c>
       <c r="L34" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E35" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" t="s">
+        <v>204</v>
+      </c>
+      <c r="G35" t="s">
+        <v>205</v>
+      </c>
+      <c r="H35" t="s">
+        <v>206</v>
+      </c>
+      <c r="I35" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" t="s">
         <v>207</v>
       </c>
-      <c r="F35" t="s">
-        <v>208</v>
-      </c>
-      <c r="G35" t="s">
-        <v>209</v>
-      </c>
-      <c r="H35" t="s">
-        <v>210</v>
-      </c>
-      <c r="I35" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" t="s">
-        <v>211</v>
-      </c>
       <c r="L35" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -2522,7 +2526,7 @@
         <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
@@ -2534,10 +2538,10 @@
         <v>13</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I36" t="s">
         <v>16</v>
@@ -2551,25 +2555,25 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E37" t="s">
         <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s">
         <v>16</v>
@@ -2578,33 +2582,33 @@
         <v>17</v>
       </c>
       <c r="K37" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L37" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E38" t="s">
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G38" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H38" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I38" t="s">
         <v>16</v>
@@ -2613,33 +2617,33 @@
         <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L38" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
         <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H39" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I39" t="s">
         <v>16</v>
@@ -2648,380 +2652,380 @@
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" t="s">
+        <v>204</v>
+      </c>
+      <c r="G40" t="s">
+        <v>205</v>
+      </c>
+      <c r="H40" t="s">
         <v>206</v>
       </c>
-      <c r="E40" t="s">
+      <c r="I40" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" t="s">
         <v>207</v>
       </c>
-      <c r="F40" t="s">
+      <c r="L40" t="s">
         <v>208</v>
-      </c>
-      <c r="G40" t="s">
-        <v>209</v>
-      </c>
-      <c r="H40" t="s">
-        <v>210</v>
-      </c>
-      <c r="I40" t="s">
-        <v>26</v>
-      </c>
-      <c r="J40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" t="s">
-        <v>211</v>
-      </c>
-      <c r="L40" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="s">
+        <v>204</v>
+      </c>
+      <c r="G41" t="s">
+        <v>205</v>
+      </c>
+      <c r="H41" t="s">
+        <v>206</v>
+      </c>
+      <c r="I41" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" t="s">
         <v>207</v>
       </c>
-      <c r="F41" t="s">
-        <v>208</v>
-      </c>
-      <c r="G41" t="s">
-        <v>209</v>
-      </c>
-      <c r="H41" t="s">
-        <v>210</v>
-      </c>
-      <c r="I41" t="s">
-        <v>26</v>
-      </c>
-      <c r="J41" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" t="s">
-        <v>211</v>
-      </c>
       <c r="L41" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" t="s">
+        <v>204</v>
+      </c>
+      <c r="G42" t="s">
+        <v>205</v>
+      </c>
+      <c r="H42" t="s">
+        <v>206</v>
+      </c>
+      <c r="I42" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" t="s">
         <v>207</v>
       </c>
-      <c r="F42" t="s">
-        <v>208</v>
-      </c>
-      <c r="G42" t="s">
-        <v>209</v>
-      </c>
-      <c r="H42" t="s">
-        <v>210</v>
-      </c>
-      <c r="I42" t="s">
-        <v>26</v>
-      </c>
-      <c r="J42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" t="s">
-        <v>211</v>
-      </c>
       <c r="L42" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" t="s">
         <v>204</v>
       </c>
-      <c r="B43" t="s">
+      <c r="G43" t="s">
         <v>205</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="H43" t="s">
         <v>206</v>
       </c>
-      <c r="E43" t="s">
+      <c r="I43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" t="s">
         <v>207</v>
       </c>
-      <c r="F43" t="s">
+      <c r="L43" t="s">
         <v>208</v>
-      </c>
-      <c r="G43" t="s">
-        <v>209</v>
-      </c>
-      <c r="H43" t="s">
-        <v>210</v>
-      </c>
-      <c r="I43" t="s">
-        <v>26</v>
-      </c>
-      <c r="J43" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" t="s">
-        <v>211</v>
-      </c>
-      <c r="L43" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E44" t="s">
+        <v>203</v>
+      </c>
+      <c r="F44" t="s">
+        <v>204</v>
+      </c>
+      <c r="G44" t="s">
         <v>205</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="H44" t="s">
+        <v>206</v>
+      </c>
+      <c r="I44" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" t="s">
         <v>207</v>
       </c>
-      <c r="F44" t="s">
-        <v>208</v>
-      </c>
-      <c r="G44" t="s">
-        <v>209</v>
-      </c>
-      <c r="H44" t="s">
-        <v>210</v>
-      </c>
-      <c r="I44" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" t="s">
-        <v>211</v>
-      </c>
       <c r="L44" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I45" t="s">
         <v>16</v>
       </c>
       <c r="J45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K45" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L45" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E46" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F46" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K46" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E47" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J47" t="s">
         <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L47" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F48" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J49" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K49" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L49" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E50" t="s">
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G50" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s">
         <v>16</v>
@@ -3030,33 +3034,33 @@
         <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L50" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E51" t="s">
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G51" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H51" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I51" t="s">
         <v>16</v>
@@ -3065,30 +3069,30 @@
         <v>17</v>
       </c>
       <c r="K51" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L51" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E52" t="s">
+        <v>127</v>
+      </c>
+      <c r="G52" t="s">
+        <v>122</v>
+      </c>
+      <c r="H52" t="s">
         <v>123</v>
-      </c>
-      <c r="E52" t="s">
-        <v>131</v>
-      </c>
-      <c r="G52" t="s">
-        <v>126</v>
-      </c>
-      <c r="H52" t="s">
-        <v>127</v>
       </c>
       <c r="I52" t="s">
         <v>16</v>
@@ -3097,33 +3101,33 @@
         <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L52" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E53" t="s">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G53" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H53" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I53" t="s">
         <v>16</v>
@@ -3132,255 +3136,255 @@
         <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L53" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E54" t="s">
+        <v>120</v>
+      </c>
+      <c r="F54" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" t="s">
+        <v>141</v>
+      </c>
+      <c r="H54" t="s">
+        <v>142</v>
+      </c>
+      <c r="I54" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" t="s">
         <v>143</v>
       </c>
-      <c r="E54" t="s">
-        <v>124</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="K54" t="s">
+        <v>95</v>
+      </c>
+      <c r="L54" t="s">
         <v>144</v>
-      </c>
-      <c r="G54" t="s">
-        <v>145</v>
-      </c>
-      <c r="H54" t="s">
-        <v>146</v>
-      </c>
-      <c r="I54" t="s">
-        <v>26</v>
-      </c>
-      <c r="J54" t="s">
-        <v>147</v>
-      </c>
-      <c r="K54" t="s">
-        <v>99</v>
-      </c>
-      <c r="L54" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" t="s">
+        <v>148</v>
+      </c>
+      <c r="G55" t="s">
+        <v>149</v>
+      </c>
+      <c r="H55" t="s">
+        <v>150</v>
+      </c>
+      <c r="I55" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" t="s">
+        <v>143</v>
+      </c>
+      <c r="K55" t="s">
         <v>151</v>
       </c>
-      <c r="E55" t="s">
-        <v>124</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="L55" t="s">
         <v>152</v>
-      </c>
-      <c r="G55" t="s">
-        <v>153</v>
-      </c>
-      <c r="H55" t="s">
-        <v>154</v>
-      </c>
-      <c r="I55" t="s">
-        <v>26</v>
-      </c>
-      <c r="J55" t="s">
-        <v>147</v>
-      </c>
-      <c r="K55" t="s">
-        <v>155</v>
-      </c>
-      <c r="L55" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" t="s">
+        <v>156</v>
+      </c>
+      <c r="F56" t="s">
+        <v>157</v>
+      </c>
+      <c r="G56" t="s">
+        <v>158</v>
+      </c>
+      <c r="H56" t="s">
         <v>159</v>
       </c>
-      <c r="E56" t="s">
+      <c r="I56" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" t="s">
         <v>160</v>
       </c>
-      <c r="F56" t="s">
+      <c r="L56" t="s">
         <v>161</v>
-      </c>
-      <c r="G56" t="s">
-        <v>162</v>
-      </c>
-      <c r="H56" t="s">
-        <v>163</v>
-      </c>
-      <c r="I56" t="s">
-        <v>26</v>
-      </c>
-      <c r="J56" t="s">
-        <v>17</v>
-      </c>
-      <c r="K56" t="s">
-        <v>164</v>
-      </c>
-      <c r="L56" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" t="s">
+        <v>120</v>
+      </c>
+      <c r="F57" t="s">
+        <v>194</v>
+      </c>
+      <c r="G57" t="s">
+        <v>195</v>
+      </c>
+      <c r="H57" t="s">
+        <v>196</v>
+      </c>
+      <c r="I57" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" t="s">
         <v>197</v>
       </c>
-      <c r="E57" t="s">
-        <v>124</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="L57" t="s">
         <v>198</v>
-      </c>
-      <c r="G57" t="s">
-        <v>199</v>
-      </c>
-      <c r="H57" t="s">
-        <v>200</v>
-      </c>
-      <c r="I57" t="s">
-        <v>26</v>
-      </c>
-      <c r="J57" t="s">
-        <v>17</v>
-      </c>
-      <c r="K57" t="s">
-        <v>201</v>
-      </c>
-      <c r="L57" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E58" t="s">
+        <v>203</v>
+      </c>
+      <c r="F58" t="s">
+        <v>204</v>
+      </c>
+      <c r="G58" t="s">
+        <v>205</v>
+      </c>
+      <c r="H58" t="s">
         <v>206</v>
       </c>
-      <c r="E58" t="s">
+      <c r="I58" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58" t="s">
         <v>207</v>
       </c>
-      <c r="F58" t="s">
+      <c r="L58" t="s">
         <v>208</v>
-      </c>
-      <c r="G58" t="s">
-        <v>209</v>
-      </c>
-      <c r="H58" t="s">
-        <v>210</v>
-      </c>
-      <c r="I58" t="s">
-        <v>26</v>
-      </c>
-      <c r="J58" t="s">
-        <v>17</v>
-      </c>
-      <c r="K58" t="s">
-        <v>211</v>
-      </c>
-      <c r="L58" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E59" t="s">
+        <v>203</v>
+      </c>
+      <c r="F59" t="s">
+        <v>204</v>
+      </c>
+      <c r="G59" t="s">
+        <v>205</v>
+      </c>
+      <c r="H59" t="s">
+        <v>206</v>
+      </c>
+      <c r="I59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" t="s">
         <v>207</v>
       </c>
-      <c r="F59" t="s">
-        <v>208</v>
-      </c>
-      <c r="G59" t="s">
-        <v>209</v>
-      </c>
-      <c r="H59" t="s">
-        <v>210</v>
-      </c>
-      <c r="I59" t="s">
-        <v>26</v>
-      </c>
-      <c r="J59" t="s">
-        <v>17</v>
-      </c>
-      <c r="K59" t="s">
-        <v>211</v>
-      </c>
       <c r="L59" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E60" t="s">
+        <v>203</v>
+      </c>
+      <c r="F60" t="s">
+        <v>204</v>
+      </c>
+      <c r="G60" t="s">
+        <v>205</v>
+      </c>
+      <c r="H60" t="s">
+        <v>206</v>
+      </c>
+      <c r="I60" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" t="s">
         <v>207</v>
       </c>
-      <c r="F60" t="s">
-        <v>208</v>
-      </c>
-      <c r="G60" t="s">
-        <v>209</v>
-      </c>
-      <c r="H60" t="s">
-        <v>210</v>
-      </c>
-      <c r="I60" t="s">
-        <v>26</v>
-      </c>
-      <c r="J60" t="s">
-        <v>17</v>
-      </c>
-      <c r="K60" t="s">
-        <v>211</v>
-      </c>
       <c r="L60" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
@@ -3388,22 +3392,22 @@
         <v>101</v>
       </c>
       <c r="B61" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E61" t="s">
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G61" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I61" t="s">
         <v>16</v>
@@ -3412,10 +3416,10 @@
         <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
@@ -3423,22 +3427,22 @@
         <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" t="s">
+        <v>120</v>
+      </c>
+      <c r="F62" t="s">
+        <v>121</v>
+      </c>
+      <c r="G62" t="s">
+        <v>122</v>
+      </c>
+      <c r="H62" t="s">
         <v>123</v>
-      </c>
-      <c r="E62" t="s">
-        <v>124</v>
-      </c>
-      <c r="F62" t="s">
-        <v>125</v>
-      </c>
-      <c r="G62" t="s">
-        <v>126</v>
-      </c>
-      <c r="H62" t="s">
-        <v>127</v>
       </c>
       <c r="I62" t="s">
         <v>16</v>
@@ -3447,10 +3451,10 @@
         <v>17</v>
       </c>
       <c r="K62" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L62" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -3458,16 +3462,16 @@
         <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D63" s="2">
         <v>760</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I63" t="s">
         <v>16</v>
@@ -3476,7 +3480,7 @@
         <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -3484,34 +3488,34 @@
         <v>104</v>
       </c>
       <c r="B64" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D64" s="2">
         <v>948</v>
       </c>
       <c r="E64" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F64" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J64" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K64" t="s">
+        <v>228</v>
+      </c>
+      <c r="L64" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="L64" s="5" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -3519,34 +3523,34 @@
         <v>105</v>
       </c>
       <c r="B65" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="F65" t="s">
+        <v>194</v>
+      </c>
+      <c r="G65" t="s">
+        <v>195</v>
+      </c>
+      <c r="H65" t="s">
+        <v>196</v>
+      </c>
+      <c r="I65" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" t="s">
+        <v>197</v>
+      </c>
+      <c r="L65" t="s">
         <v>198</v>
-      </c>
-      <c r="G65" t="s">
-        <v>199</v>
-      </c>
-      <c r="H65" t="s">
-        <v>200</v>
-      </c>
-      <c r="I65" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K65" t="s">
-        <v>201</v>
-      </c>
-      <c r="L65" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -3554,34 +3558,34 @@
         <v>106</v>
       </c>
       <c r="B66" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F66" t="s">
+        <v>204</v>
+      </c>
+      <c r="G66" t="s">
+        <v>205</v>
+      </c>
+      <c r="H66" t="s">
+        <v>206</v>
+      </c>
+      <c r="I66" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" t="s">
+        <v>207</v>
+      </c>
+      <c r="L66" t="s">
         <v>208</v>
-      </c>
-      <c r="G66" t="s">
-        <v>209</v>
-      </c>
-      <c r="H66" t="s">
-        <v>210</v>
-      </c>
-      <c r="I66" t="s">
-        <v>26</v>
-      </c>
-      <c r="J66" t="s">
-        <v>17</v>
-      </c>
-      <c r="K66" t="s">
-        <v>211</v>
-      </c>
-      <c r="L66" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -3589,34 +3593,34 @@
         <v>107</v>
       </c>
       <c r="B67" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F67" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G67" t="s">
+        <v>165</v>
+      </c>
+      <c r="H67" t="s">
+        <v>166</v>
+      </c>
+      <c r="I67" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" t="s">
+        <v>167</v>
+      </c>
+      <c r="K67" t="s">
+        <v>168</v>
+      </c>
+      <c r="L67" t="s">
         <v>169</v>
-      </c>
-      <c r="H67" t="s">
-        <v>170</v>
-      </c>
-      <c r="I67" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" t="s">
-        <v>171</v>
-      </c>
-      <c r="K67" t="s">
-        <v>172</v>
-      </c>
-      <c r="L67" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -3624,34 +3628,34 @@
         <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F68" t="s">
+        <v>140</v>
+      </c>
+      <c r="G68" t="s">
+        <v>141</v>
+      </c>
+      <c r="H68" t="s">
+        <v>142</v>
+      </c>
+      <c r="I68" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" t="s">
+        <v>143</v>
+      </c>
+      <c r="K68" t="s">
+        <v>95</v>
+      </c>
+      <c r="L68" t="s">
         <v>144</v>
-      </c>
-      <c r="G68" t="s">
-        <v>145</v>
-      </c>
-      <c r="H68" t="s">
-        <v>146</v>
-      </c>
-      <c r="I68" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" t="s">
-        <v>147</v>
-      </c>
-      <c r="K68" t="s">
-        <v>99</v>
-      </c>
-      <c r="L68" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-1301-Bus.xlsx
+++ b/db/A7XLK-1301-Bus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08663BB9-B552-F648-96F2-8FB1C3DCD310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5566333-3ABC-8241-8BB0-80722525A231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1940" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="3240" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="261">
   <si>
     <t>No</t>
   </si>
@@ -824,6 +824,22 @@
   </si>
   <si>
     <t xml:space="preserve">202 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/Route/StopsOfRoute?routeid=0400096610</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/Route/StopsOfRoute?routeid=0400096710</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/Route/StopsOfRoute?routeid=0400093710</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/Route/StopsOfRoute?routeid=0400092010</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3534,11 +3550,11 @@
       <c r="F65" t="s">
         <v>194</v>
       </c>
-      <c r="G65" t="s">
-        <v>195</v>
-      </c>
-      <c r="H65" t="s">
-        <v>196</v>
+      <c r="G65" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="I65" t="s">
         <v>25</v>
@@ -3569,11 +3585,11 @@
       <c r="F66" t="s">
         <v>204</v>
       </c>
-      <c r="G66" t="s">
-        <v>205</v>
-      </c>
-      <c r="H66" t="s">
-        <v>206</v>
+      <c r="G66" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="I66" t="s">
         <v>25</v>
@@ -3604,11 +3620,11 @@
       <c r="F67" t="s">
         <v>157</v>
       </c>
-      <c r="G67" t="s">
-        <v>165</v>
-      </c>
-      <c r="H67" t="s">
-        <v>166</v>
+      <c r="G67" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="I67" t="s">
         <v>25</v>
@@ -3639,11 +3655,11 @@
       <c r="F68" t="s">
         <v>140</v>
       </c>
-      <c r="G68" t="s">
-        <v>141</v>
-      </c>
-      <c r="H68" t="s">
-        <v>142</v>
+      <c r="G68" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="I68" t="s">
         <v>25</v>
@@ -3666,37 +3682,45 @@
   <hyperlinks>
     <hyperlink ref="L64" r:id="rId1" xr:uid="{9879FFAF-1B89-4142-BC32-5F8FF16D1C65}"/>
     <hyperlink ref="H64" r:id="rId2" xr:uid="{03C06EE7-B036-FD43-BE6D-03B1D0965FA4}"/>
-    <hyperlink ref="G64" r:id="rId3" xr:uid="{D816E695-43E8-B848-8865-24DFCE3DDE79}"/>
-    <hyperlink ref="H8" r:id="rId4" xr:uid="{B38EF02A-B2AF-7C45-90B3-3FDB0455F17E}"/>
-    <hyperlink ref="H9" r:id="rId5" xr:uid="{A1583536-1BB0-FB4F-B69B-5D53DFD19104}"/>
-    <hyperlink ref="H10" r:id="rId6" xr:uid="{600C9A84-F812-0E4F-BA2A-4CA0F3FE615C}"/>
-    <hyperlink ref="H11" r:id="rId7" xr:uid="{61C1C9BB-BA75-1F46-BF63-C986010EC06F}"/>
-    <hyperlink ref="H12" r:id="rId8" xr:uid="{F45F7B93-8634-034E-9C7E-E3DD87128229}"/>
-    <hyperlink ref="H13" r:id="rId9" xr:uid="{E62B9FDC-87D7-9B46-B497-3086B58C18C3}"/>
-    <hyperlink ref="H14" r:id="rId10" xr:uid="{31A5AAD2-57C4-9841-9B92-3613E367BF9D}"/>
-    <hyperlink ref="H15" r:id="rId11" xr:uid="{5343F1A6-B31A-C247-9064-9380FF431AB0}"/>
-    <hyperlink ref="H16" r:id="rId12" xr:uid="{F2628EE4-27D6-B04B-B7BB-A86B72067AAD}"/>
-    <hyperlink ref="H18" r:id="rId13" xr:uid="{B50369B8-AA2F-4547-B593-6205CEA577F1}"/>
-    <hyperlink ref="H45" r:id="rId14" xr:uid="{54D5D8F7-54E0-104B-95A4-9D5684440C2A}"/>
-    <hyperlink ref="H46" r:id="rId15" xr:uid="{D517414B-9453-4846-A2C4-6008C25A6E81}"/>
-    <hyperlink ref="H47" r:id="rId16" xr:uid="{4DC9BDDF-C26B-F54B-9352-F94D3940FB1F}"/>
-    <hyperlink ref="H49" r:id="rId17" xr:uid="{244B43CA-BC03-8449-AB34-832F2A4A08A6}"/>
-    <hyperlink ref="G8" r:id="rId18" xr:uid="{87BCA5E7-61AE-9343-AFBF-4949F97A1573}"/>
-    <hyperlink ref="G9" r:id="rId19" xr:uid="{EDA56214-229D-AA44-9531-B2C732F1EBFB}"/>
-    <hyperlink ref="G10" r:id="rId20" xr:uid="{1115C12E-C2EF-2D44-8331-D9F21E5FAB8B}"/>
-    <hyperlink ref="G11" r:id="rId21" xr:uid="{BE0D18CF-8989-F440-BB14-41637E2C3090}"/>
-    <hyperlink ref="G12" r:id="rId22" xr:uid="{D6BC3C80-A3EB-BB4F-BEB4-F3B6E5C92EBC}"/>
-    <hyperlink ref="G13" r:id="rId23" xr:uid="{B7CC6FE9-BB6B-8440-90D6-8AF24B1FAAE2}"/>
-    <hyperlink ref="G14" r:id="rId24" xr:uid="{A2FF1CD3-1F4F-D14C-AEBB-EE7B5C78C33B}"/>
-    <hyperlink ref="G15" r:id="rId25" xr:uid="{56D0F2CF-E77D-1E4A-B084-D982FF9FB4DD}"/>
-    <hyperlink ref="G16" r:id="rId26" xr:uid="{A22E894A-9D67-2E4E-99E8-D4A7734F9214}"/>
-    <hyperlink ref="G18" r:id="rId27" xr:uid="{219E7006-8AD1-1440-9D44-8E7CBA1935DC}"/>
-    <hyperlink ref="G45" r:id="rId28" xr:uid="{D3B084B0-B7B4-624F-83B7-A14B02B8A44A}"/>
-    <hyperlink ref="G46" r:id="rId29" xr:uid="{36C0344C-E3E2-2B4F-AB6C-248C1A361A95}"/>
-    <hyperlink ref="G47" r:id="rId30" xr:uid="{57E6CB22-2581-1849-AC3B-78064D4FE2FA}"/>
-    <hyperlink ref="G49" r:id="rId31" xr:uid="{11599548-4371-8247-A7FC-AAB26906B525}"/>
-    <hyperlink ref="H36" r:id="rId32" xr:uid="{B4964FA7-8E24-324A-B6C6-E13582B429A9}"/>
-    <hyperlink ref="G36" r:id="rId33" xr:uid="{1EED94F5-6694-824D-85B0-338E29E72824}"/>
+    <hyperlink ref="H8" r:id="rId3" xr:uid="{B38EF02A-B2AF-7C45-90B3-3FDB0455F17E}"/>
+    <hyperlink ref="H9" r:id="rId4" xr:uid="{A1583536-1BB0-FB4F-B69B-5D53DFD19104}"/>
+    <hyperlink ref="H10" r:id="rId5" xr:uid="{600C9A84-F812-0E4F-BA2A-4CA0F3FE615C}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{61C1C9BB-BA75-1F46-BF63-C986010EC06F}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{F45F7B93-8634-034E-9C7E-E3DD87128229}"/>
+    <hyperlink ref="H13" r:id="rId8" xr:uid="{E62B9FDC-87D7-9B46-B497-3086B58C18C3}"/>
+    <hyperlink ref="H14" r:id="rId9" xr:uid="{31A5AAD2-57C4-9841-9B92-3613E367BF9D}"/>
+    <hyperlink ref="H15" r:id="rId10" xr:uid="{5343F1A6-B31A-C247-9064-9380FF431AB0}"/>
+    <hyperlink ref="H16" r:id="rId11" xr:uid="{F2628EE4-27D6-B04B-B7BB-A86B72067AAD}"/>
+    <hyperlink ref="H18" r:id="rId12" xr:uid="{B50369B8-AA2F-4547-B593-6205CEA577F1}"/>
+    <hyperlink ref="H45" r:id="rId13" xr:uid="{54D5D8F7-54E0-104B-95A4-9D5684440C2A}"/>
+    <hyperlink ref="H46" r:id="rId14" xr:uid="{D517414B-9453-4846-A2C4-6008C25A6E81}"/>
+    <hyperlink ref="H47" r:id="rId15" xr:uid="{4DC9BDDF-C26B-F54B-9352-F94D3940FB1F}"/>
+    <hyperlink ref="H49" r:id="rId16" xr:uid="{244B43CA-BC03-8449-AB34-832F2A4A08A6}"/>
+    <hyperlink ref="G8" r:id="rId17" xr:uid="{87BCA5E7-61AE-9343-AFBF-4949F97A1573}"/>
+    <hyperlink ref="G9" r:id="rId18" xr:uid="{EDA56214-229D-AA44-9531-B2C732F1EBFB}"/>
+    <hyperlink ref="G10" r:id="rId19" xr:uid="{1115C12E-C2EF-2D44-8331-D9F21E5FAB8B}"/>
+    <hyperlink ref="G11" r:id="rId20" xr:uid="{BE0D18CF-8989-F440-BB14-41637E2C3090}"/>
+    <hyperlink ref="G12" r:id="rId21" xr:uid="{D6BC3C80-A3EB-BB4F-BEB4-F3B6E5C92EBC}"/>
+    <hyperlink ref="G13" r:id="rId22" xr:uid="{B7CC6FE9-BB6B-8440-90D6-8AF24B1FAAE2}"/>
+    <hyperlink ref="G14" r:id="rId23" xr:uid="{A2FF1CD3-1F4F-D14C-AEBB-EE7B5C78C33B}"/>
+    <hyperlink ref="G15" r:id="rId24" xr:uid="{56D0F2CF-E77D-1E4A-B084-D982FF9FB4DD}"/>
+    <hyperlink ref="G16" r:id="rId25" xr:uid="{A22E894A-9D67-2E4E-99E8-D4A7734F9214}"/>
+    <hyperlink ref="G18" r:id="rId26" xr:uid="{219E7006-8AD1-1440-9D44-8E7CBA1935DC}"/>
+    <hyperlink ref="G45" r:id="rId27" xr:uid="{D3B084B0-B7B4-624F-83B7-A14B02B8A44A}"/>
+    <hyperlink ref="G46" r:id="rId28" xr:uid="{36C0344C-E3E2-2B4F-AB6C-248C1A361A95}"/>
+    <hyperlink ref="G47" r:id="rId29" xr:uid="{57E6CB22-2581-1849-AC3B-78064D4FE2FA}"/>
+    <hyperlink ref="G49" r:id="rId30" xr:uid="{11599548-4371-8247-A7FC-AAB26906B525}"/>
+    <hyperlink ref="H36" r:id="rId31" xr:uid="{B4964FA7-8E24-324A-B6C6-E13582B429A9}"/>
+    <hyperlink ref="G36" r:id="rId32" xr:uid="{1EED94F5-6694-824D-85B0-338E29E72824}"/>
+    <hyperlink ref="G64" r:id="rId33" xr:uid="{D816E695-43E8-B848-8865-24DFCE3DDE79}"/>
+    <hyperlink ref="G65" r:id="rId34" xr:uid="{34D3F511-1670-9841-99B2-953E02FA1AE1}"/>
+    <hyperlink ref="H65" r:id="rId35" xr:uid="{DA96417C-FDE3-254A-8B82-77B45C7B4B0A}"/>
+    <hyperlink ref="G66" r:id="rId36" xr:uid="{F755F3FE-5192-7148-8B84-FAD83C2FAC7D}"/>
+    <hyperlink ref="H66" r:id="rId37" xr:uid="{F8D913D0-50CB-B740-9F5B-1FBF1DA7653B}"/>
+    <hyperlink ref="G67" r:id="rId38" xr:uid="{9719D29F-EA7A-E54B-B6E0-4785F1717AEA}"/>
+    <hyperlink ref="H67" r:id="rId39" xr:uid="{95858069-9D80-594F-B9FD-0A75CABE0EF9}"/>
+    <hyperlink ref="G68" r:id="rId40" xr:uid="{FC54AB93-01C5-1C4B-B9DA-293E73A2B623}"/>
+    <hyperlink ref="H68" r:id="rId41" xr:uid="{31357D9A-3DF1-EA4F-8040-DA5A17984CA0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-1301-Bus.xlsx
+++ b/db/A7XLK-1301-Bus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5566333-3ABC-8241-8BB0-80722525A231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D1F6E-BC76-FF45-ABE6-B840D4BD5CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="3240" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="460" yWindow="9860" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="267">
   <si>
     <t>No</t>
   </si>
@@ -840,6 +840,30 @@
   </si>
   <si>
     <t>https://ebus.gov.taipei/Route/StopsOfRoute?routeid=0400092010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/Route/StopsOfRoute?routeid=0400076000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/MapOverview?nid=0400076000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/MapOverview?nid=0400096610</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/MapOverview?nid=0400096710</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/MapOverview?nid=0400093710</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ebus.gov.taipei/MapOverview?nid=0400092010</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3489,6 +3513,12 @@
       <c r="F63" s="4" t="s">
         <v>226</v>
       </c>
+      <c r="G63" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>261</v>
+      </c>
       <c r="I63" t="s">
         <v>16</v>
       </c>
@@ -3497,6 +3527,9 @@
       </c>
       <c r="K63" t="s">
         <v>227</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -3565,8 +3598,8 @@
       <c r="K65" t="s">
         <v>197</v>
       </c>
-      <c r="L65" t="s">
-        <v>198</v>
+      <c r="L65" s="5" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -3600,8 +3633,8 @@
       <c r="K66" t="s">
         <v>207</v>
       </c>
-      <c r="L66" t="s">
-        <v>208</v>
+      <c r="L66" s="5" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -3635,8 +3668,8 @@
       <c r="K67" t="s">
         <v>168</v>
       </c>
-      <c r="L67" t="s">
-        <v>169</v>
+      <c r="L67" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -3670,8 +3703,8 @@
       <c r="K68" t="s">
         <v>95</v>
       </c>
-      <c r="L68" t="s">
-        <v>144</v>
+      <c r="L68" s="5" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3721,6 +3754,13 @@
     <hyperlink ref="H67" r:id="rId39" xr:uid="{95858069-9D80-594F-B9FD-0A75CABE0EF9}"/>
     <hyperlink ref="G68" r:id="rId40" xr:uid="{FC54AB93-01C5-1C4B-B9DA-293E73A2B623}"/>
     <hyperlink ref="H68" r:id="rId41" xr:uid="{31357D9A-3DF1-EA4F-8040-DA5A17984CA0}"/>
+    <hyperlink ref="G63" r:id="rId42" xr:uid="{3D46C562-2438-1849-954B-812FC557FB46}"/>
+    <hyperlink ref="H63" r:id="rId43" xr:uid="{EF72BC12-7B2B-8D46-8F08-B9C729976F96}"/>
+    <hyperlink ref="L63" r:id="rId44" xr:uid="{C47BF7DA-3F12-2846-AD8A-BA5412053042}"/>
+    <hyperlink ref="L65" r:id="rId45" xr:uid="{0803A5C6-46A6-A347-A3F0-9BB2D3483CDF}"/>
+    <hyperlink ref="L66" r:id="rId46" xr:uid="{D7E0A4ED-80B7-0143-AA0A-E26EC1615AA4}"/>
+    <hyperlink ref="L67" r:id="rId47" xr:uid="{D5C94E95-29D8-1849-A8F4-117BC19CE876}"/>
+    <hyperlink ref="L68" r:id="rId48" xr:uid="{65BE0C33-05C3-BD44-B9CE-536D3B6CB9E0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>
